--- a/Japanese Database JLPT Sensei - N5.xlsx
+++ b/Japanese Database JLPT Sensei - N5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\USMAN\Project\Learn Japanese Web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2865C1AD-F294-44A8-9017-DDBF3139EF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3100CD-B702-4A2E-B8BB-69A6B324659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{A915BC42-6F5B-4AB0-B6BC-85429C4851F3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="1537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3871" uniqueCount="2457">
   <si>
     <t>level</t>
   </si>
@@ -4636,6 +4636,2766 @@
   </si>
   <si>
     <t>to get on (train, plane, bus, ship, etc.)</t>
+  </si>
+  <si>
+    <t>脱ぐ</t>
+  </si>
+  <si>
+    <t>ぬぐ</t>
+  </si>
+  <si>
+    <t>温い</t>
+  </si>
+  <si>
+    <t>ぬるい</t>
+  </si>
+  <si>
+    <t>ニュース</t>
+  </si>
+  <si>
+    <t>おばあさん</t>
+  </si>
+  <si>
+    <t>伯母さん</t>
+  </si>
+  <si>
+    <t>おばさん</t>
+  </si>
+  <si>
+    <t>お弁当</t>
+  </si>
+  <si>
+    <t>おべんとう</t>
+  </si>
+  <si>
+    <t>覚える</t>
+  </si>
+  <si>
+    <t>おぼえる</t>
+  </si>
+  <si>
+    <t>nugu</t>
+  </si>
+  <si>
+    <t>nurui</t>
+  </si>
+  <si>
+    <t>nyuusu</t>
+  </si>
+  <si>
+    <t>obaasan</t>
+  </si>
+  <si>
+    <t>obasan</t>
+  </si>
+  <si>
+    <t>obentou</t>
+  </si>
+  <si>
+    <t>oboeru</t>
+  </si>
+  <si>
+    <t>お茶</t>
+  </si>
+  <si>
+    <t>おちゃ</t>
+  </si>
+  <si>
+    <t>お風呂</t>
+  </si>
+  <si>
+    <t>おふろ</t>
+  </si>
+  <si>
+    <t>美味しい</t>
+  </si>
+  <si>
+    <t>おいしい</t>
+  </si>
+  <si>
+    <t>伯父さん</t>
+  </si>
+  <si>
+    <t>おじさん</t>
+  </si>
+  <si>
+    <t>お母さん</t>
+  </si>
+  <si>
+    <t>おかあさん</t>
+  </si>
+  <si>
+    <t>お金</t>
+  </si>
+  <si>
+    <t>おかね</t>
+  </si>
+  <si>
+    <t>お菓子</t>
+  </si>
+  <si>
+    <t>おかし</t>
+  </si>
+  <si>
+    <t>起きる</t>
+  </si>
+  <si>
+    <t>おきる</t>
+  </si>
+  <si>
+    <t>tea</t>
+  </si>
+  <si>
+    <t>bath</t>
+  </si>
+  <si>
+    <t>delicious</t>
+  </si>
+  <si>
+    <t>uncle; old man; mister</t>
+  </si>
+  <si>
+    <t>mother; mom; mum; ma</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>confections; sweets; candy</t>
+  </si>
+  <si>
+    <t>to take off clothes</t>
+  </si>
+  <si>
+    <t>luke warm</t>
+  </si>
+  <si>
+    <t>news</t>
+  </si>
+  <si>
+    <t>grandmother</t>
+  </si>
+  <si>
+    <t>aunt; old lady</t>
+  </si>
+  <si>
+    <t>lunch box; japanese box lunch</t>
+  </si>
+  <si>
+    <t>to remember</t>
+  </si>
+  <si>
+    <t>to get up; to wake up</t>
+  </si>
+  <si>
+    <t>ocha</t>
+  </si>
+  <si>
+    <t>ofuro</t>
+  </si>
+  <si>
+    <t>oishii</t>
+  </si>
+  <si>
+    <t>ojisan</t>
+  </si>
+  <si>
+    <t>okaasan</t>
+  </si>
+  <si>
+    <t>okane</t>
+  </si>
+  <si>
+    <t>okashi</t>
+  </si>
+  <si>
+    <t>okiru</t>
+  </si>
+  <si>
+    <t>verb, ichidan verb</t>
+  </si>
+  <si>
+    <t>置く</t>
+  </si>
+  <si>
+    <t>おく</t>
+  </si>
+  <si>
+    <t>奥さん</t>
+  </si>
+  <si>
+    <t>おくさん</t>
+  </si>
+  <si>
+    <t>お巡りさん</t>
+  </si>
+  <si>
+    <t>おまわりさん</t>
+  </si>
+  <si>
+    <t>おもい</t>
+  </si>
+  <si>
+    <t>重い</t>
+  </si>
+  <si>
+    <t>面白い</t>
+  </si>
+  <si>
+    <t>おもしろい</t>
+  </si>
+  <si>
+    <t>同じ</t>
+  </si>
+  <si>
+    <t>おなじ</t>
+  </si>
+  <si>
+    <t>お腹</t>
+  </si>
+  <si>
+    <t>おなか</t>
+  </si>
+  <si>
+    <t>oku</t>
+  </si>
+  <si>
+    <t>okusan</t>
+  </si>
+  <si>
+    <t>omawarisan</t>
+  </si>
+  <si>
+    <t>omoi</t>
+  </si>
+  <si>
+    <t>omoshiroi</t>
+  </si>
+  <si>
+    <t>onaji</t>
+  </si>
+  <si>
+    <t>onaka</t>
+  </si>
+  <si>
+    <t>to put; to place</t>
+  </si>
+  <si>
+    <t>wife; your wife; his wife</t>
+  </si>
+  <si>
+    <t>police officer (friendly term for policeman)</t>
+  </si>
+  <si>
+    <t>heavy</t>
+  </si>
+  <si>
+    <t>interesting</t>
+  </si>
+  <si>
+    <t>same</t>
+  </si>
+  <si>
+    <t>stomach</t>
+  </si>
+  <si>
+    <t>お姉さん</t>
+  </si>
+  <si>
+    <t>おねえさん</t>
+  </si>
+  <si>
+    <t>音楽</t>
+  </si>
+  <si>
+    <t>おんがく</t>
+  </si>
+  <si>
+    <t>お兄さん</t>
+  </si>
+  <si>
+    <t>おにいさん</t>
+  </si>
+  <si>
+    <t>女</t>
+  </si>
+  <si>
+    <t>女の子</t>
+  </si>
+  <si>
+    <t>おんなのこ</t>
+  </si>
+  <si>
+    <t>多い</t>
+  </si>
+  <si>
+    <t>おおい</t>
+  </si>
+  <si>
+    <t>大きい</t>
+  </si>
+  <si>
+    <t>おおきい</t>
+  </si>
+  <si>
+    <t>おおきな</t>
+  </si>
+  <si>
+    <t>大きな</t>
+  </si>
+  <si>
+    <t>oneesan</t>
+  </si>
+  <si>
+    <t>ongaku</t>
+  </si>
+  <si>
+    <t>oniisan</t>
+  </si>
+  <si>
+    <t>onna</t>
+  </si>
+  <si>
+    <t>おんな</t>
+  </si>
+  <si>
+    <t>onnanoko</t>
+  </si>
+  <si>
+    <t>ooi</t>
+  </si>
+  <si>
+    <t>ookii</t>
+  </si>
+  <si>
+    <t>ookina</t>
+  </si>
+  <si>
+    <t>noun, prefix</t>
+  </si>
+  <si>
+    <t>noun, expression</t>
+  </si>
+  <si>
+    <t>elder sister; young lady; miss; ma'am</t>
+  </si>
+  <si>
+    <t>music</t>
+  </si>
+  <si>
+    <t>older brother; elder brother; young man; buddy</t>
+  </si>
+  <si>
+    <t>woman; female sex</t>
+  </si>
+  <si>
+    <t>girl; daughter; young women</t>
+  </si>
+  <si>
+    <t>many; numerous; a lot; large quantity; frequent</t>
+  </si>
+  <si>
+    <t>big; large; great; important</t>
+  </si>
+  <si>
+    <t>big; large; great</t>
+  </si>
+  <si>
+    <t>大勢</t>
+  </si>
+  <si>
+    <t>おおぜい</t>
+  </si>
+  <si>
+    <t>降りる</t>
+  </si>
+  <si>
+    <t>おりる</t>
+  </si>
+  <si>
+    <t>お酒</t>
+  </si>
+  <si>
+    <t>おさけ</t>
+  </si>
+  <si>
+    <t>お皿</t>
+  </si>
+  <si>
+    <t>おさら</t>
+  </si>
+  <si>
+    <t>教える</t>
+  </si>
+  <si>
+    <t>おしえる</t>
+  </si>
+  <si>
+    <t>遅い</t>
+  </si>
+  <si>
+    <t>おそい</t>
+  </si>
+  <si>
+    <t>押す</t>
+  </si>
+  <si>
+    <t>おす</t>
+  </si>
+  <si>
+    <t>oozei</t>
+  </si>
+  <si>
+    <t>oriru</t>
+  </si>
+  <si>
+    <t>osake</t>
+  </si>
+  <si>
+    <t>osara</t>
+  </si>
+  <si>
+    <t>oshieru</t>
+  </si>
+  <si>
+    <t>osoi</t>
+  </si>
+  <si>
+    <t>osu</t>
+  </si>
+  <si>
+    <t>crowd of people; great number of people</t>
+  </si>
+  <si>
+    <t>to get off</t>
+  </si>
+  <si>
+    <t>alcohol</t>
+  </si>
+  <si>
+    <t>plate; dish</t>
+  </si>
+  <si>
+    <t>to teach</t>
+  </si>
+  <si>
+    <t>slow; time-consuming; late</t>
+  </si>
+  <si>
+    <t>to push; to press</t>
+  </si>
+  <si>
+    <t>お手洗い</t>
+  </si>
+  <si>
+    <t>男</t>
+  </si>
+  <si>
+    <t>男の子</t>
+  </si>
+  <si>
+    <t>大人</t>
+  </si>
+  <si>
+    <t>一昨日</t>
+  </si>
+  <si>
+    <t>一昨年</t>
+  </si>
+  <si>
+    <t>お父さん</t>
+  </si>
+  <si>
+    <t>弟</t>
+  </si>
+  <si>
+    <t>おてあらい</t>
+  </si>
+  <si>
+    <t>おとこ</t>
+  </si>
+  <si>
+    <t>おとこのこ</t>
+  </si>
+  <si>
+    <t>おとな</t>
+  </si>
+  <si>
+    <t>おととい</t>
+  </si>
+  <si>
+    <t>おととし</t>
+  </si>
+  <si>
+    <t>おとうさん</t>
+  </si>
+  <si>
+    <t>おとうと</t>
+  </si>
+  <si>
+    <t>otearai</t>
+  </si>
+  <si>
+    <t>otoko</t>
+  </si>
+  <si>
+    <t>otokonoko</t>
+  </si>
+  <si>
+    <t>otona</t>
+  </si>
+  <si>
+    <t>ototoi</t>
+  </si>
+  <si>
+    <t>ototoshi</t>
+  </si>
+  <si>
+    <t>otousan</t>
+  </si>
+  <si>
+    <t>otouto</t>
+  </si>
+  <si>
+    <t>toilet; restroom; lavatory; bathroom</t>
+  </si>
+  <si>
+    <t>man; male</t>
+  </si>
+  <si>
+    <t>boy; male child; baby boy</t>
+  </si>
+  <si>
+    <t>adult</t>
+  </si>
+  <si>
+    <t>day before yesterday</t>
+  </si>
+  <si>
+    <t>year before last</t>
+  </si>
+  <si>
+    <t>father; dad; papa; pa; pop; daddy</t>
+  </si>
+  <si>
+    <t>younger brother</t>
+  </si>
+  <si>
+    <t>終わる</t>
+  </si>
+  <si>
+    <t>おわる</t>
+  </si>
+  <si>
+    <t>泳ぐ</t>
+  </si>
+  <si>
+    <t>およぐ</t>
+  </si>
+  <si>
+    <t>パーティー</t>
+  </si>
+  <si>
+    <t>パン</t>
+  </si>
+  <si>
+    <t>ページ</t>
+  </si>
+  <si>
+    <t>ペン</t>
+  </si>
+  <si>
+    <t>ペット</t>
+  </si>
+  <si>
+    <t>owaru</t>
+  </si>
+  <si>
+    <t>oyogu</t>
+  </si>
+  <si>
+    <t>paatii</t>
+  </si>
+  <si>
+    <t>pan</t>
+  </si>
+  <si>
+    <t>peeji</t>
+  </si>
+  <si>
+    <t>pen</t>
+  </si>
+  <si>
+    <t>petto</t>
+  </si>
+  <si>
+    <t>to finish; to end</t>
+  </si>
+  <si>
+    <t>to swim</t>
+  </si>
+  <si>
+    <t>party</t>
+  </si>
+  <si>
+    <t>bread</t>
+  </si>
+  <si>
+    <t>page</t>
+  </si>
+  <si>
+    <t>pet</t>
+  </si>
+  <si>
+    <t>ポケット</t>
+  </si>
+  <si>
+    <t>ポスト</t>
+  </si>
+  <si>
+    <t>プール</t>
+  </si>
+  <si>
+    <t>来月</t>
+  </si>
+  <si>
+    <t>らいげつ</t>
+  </si>
+  <si>
+    <t>来年</t>
+  </si>
+  <si>
+    <t>らいねん</t>
+  </si>
+  <si>
+    <t>来週</t>
+  </si>
+  <si>
+    <t>らいしゅう</t>
+  </si>
+  <si>
+    <t>ラジオ</t>
+  </si>
+  <si>
+    <t>れい</t>
+  </si>
+  <si>
+    <t>零</t>
+  </si>
+  <si>
+    <t>poketto</t>
+  </si>
+  <si>
+    <t>posuto</t>
+  </si>
+  <si>
+    <t>puuru</t>
+  </si>
+  <si>
+    <t>raigetsu</t>
+  </si>
+  <si>
+    <t>rainen</t>
+  </si>
+  <si>
+    <t>raishuu</t>
+  </si>
+  <si>
+    <t>rajio</t>
+  </si>
+  <si>
+    <t>rei</t>
+  </si>
+  <si>
+    <t>pocket</t>
+  </si>
+  <si>
+    <t>post</t>
+  </si>
+  <si>
+    <t>swimming pool</t>
+  </si>
+  <si>
+    <t>next month</t>
+  </si>
+  <si>
+    <t>next year</t>
+  </si>
+  <si>
+    <t>next week</t>
+  </si>
+  <si>
+    <t>radio</t>
+  </si>
+  <si>
+    <t>zero</t>
+  </si>
+  <si>
+    <t>冷蔵庫</t>
+  </si>
+  <si>
+    <t>れいぞうこ</t>
+  </si>
+  <si>
+    <t>レコード</t>
+  </si>
+  <si>
+    <t>練習</t>
+  </si>
+  <si>
+    <t>れんしゅう</t>
+  </si>
+  <si>
+    <t>レストラン</t>
+  </si>
+  <si>
+    <t>立派</t>
+  </si>
+  <si>
+    <t>りっぱ</t>
+  </si>
+  <si>
+    <t>六</t>
+  </si>
+  <si>
+    <t>ろく</t>
+  </si>
+  <si>
+    <t>廊下</t>
+  </si>
+  <si>
+    <t>ろうか</t>
+  </si>
+  <si>
+    <t>旅行</t>
+  </si>
+  <si>
+    <t>りょこう</t>
+  </si>
+  <si>
+    <t>reizouko</t>
+  </si>
+  <si>
+    <t>rekoodo</t>
+  </si>
+  <si>
+    <t>renshuu</t>
+  </si>
+  <si>
+    <t>resutoran</t>
+  </si>
+  <si>
+    <t>rippa</t>
+  </si>
+  <si>
+    <t>roku</t>
+  </si>
+  <si>
+    <t>rouka</t>
+  </si>
+  <si>
+    <t>ryokou</t>
+  </si>
+  <si>
+    <t>refrigerator</t>
+  </si>
+  <si>
+    <t>record</t>
+  </si>
+  <si>
+    <t>practice; practicing</t>
+  </si>
+  <si>
+    <t>restaurant</t>
+  </si>
+  <si>
+    <t>splendid</t>
+  </si>
+  <si>
+    <t>corridor; hallway; passageway</t>
+  </si>
+  <si>
+    <t>travel; trip; journey; excursion; tour</t>
+  </si>
+  <si>
+    <t>料理</t>
+  </si>
+  <si>
+    <t>りょうり</t>
+  </si>
+  <si>
+    <t>両親</t>
+  </si>
+  <si>
+    <t>りょうしん</t>
+  </si>
+  <si>
+    <t>留学生</t>
+  </si>
+  <si>
+    <t>りゅうがくせい</t>
+  </si>
+  <si>
+    <t>さあ</t>
+  </si>
+  <si>
+    <t>財布</t>
+  </si>
+  <si>
+    <t>さいふ</t>
+  </si>
+  <si>
+    <t>魚</t>
+  </si>
+  <si>
+    <t>さかな</t>
+  </si>
+  <si>
+    <t>先</t>
+  </si>
+  <si>
+    <t>さき</t>
+  </si>
+  <si>
+    <t>ryouri</t>
+  </si>
+  <si>
+    <t>ryoushin</t>
+  </si>
+  <si>
+    <t>ryuugakusei</t>
+  </si>
+  <si>
+    <t>saa</t>
+  </si>
+  <si>
+    <t>saifu</t>
+  </si>
+  <si>
+    <t>sakana</t>
+  </si>
+  <si>
+    <t>saki</t>
+  </si>
+  <si>
+    <t>noun, prefix, suffix</t>
+  </si>
+  <si>
+    <t>cuisine</t>
+  </si>
+  <si>
+    <t>parents; both parents</t>
+  </si>
+  <si>
+    <t>overseas student; exchange student</t>
+  </si>
+  <si>
+    <t>well..</t>
+  </si>
+  <si>
+    <t>purse; wallet</t>
+  </si>
+  <si>
+    <t>fish</t>
+  </si>
+  <si>
+    <t>previous; prior; first; earlier</t>
+  </si>
+  <si>
+    <t>咲く</t>
+  </si>
+  <si>
+    <t>さく</t>
+  </si>
+  <si>
+    <t>作文</t>
+  </si>
+  <si>
+    <t>さくぶん</t>
+  </si>
+  <si>
+    <t>寒い</t>
+  </si>
+  <si>
+    <t>さむい</t>
+  </si>
+  <si>
+    <t>三</t>
+  </si>
+  <si>
+    <t>さん</t>
+  </si>
+  <si>
+    <t>散歩</t>
+  </si>
+  <si>
+    <t>さんぽ</t>
+  </si>
+  <si>
+    <t>再来年</t>
+  </si>
+  <si>
+    <t>さらいねん</t>
+  </si>
+  <si>
+    <t>差す</t>
+  </si>
+  <si>
+    <t>さす</t>
+  </si>
+  <si>
+    <t>saku</t>
+  </si>
+  <si>
+    <t>sakubun</t>
+  </si>
+  <si>
+    <t>samui</t>
+  </si>
+  <si>
+    <t>san</t>
+  </si>
+  <si>
+    <t>sanpo</t>
+  </si>
+  <si>
+    <t>sarainen</t>
+  </si>
+  <si>
+    <t>sasu</t>
+  </si>
+  <si>
+    <t>to bloom</t>
+  </si>
+  <si>
+    <t>writing; composition</t>
+  </si>
+  <si>
+    <t>cold</t>
+  </si>
+  <si>
+    <t>walk; stroll</t>
+  </si>
+  <si>
+    <t>year after next</t>
+  </si>
+  <si>
+    <t>to stretch out hands; to raise an umbrella</t>
+  </si>
+  <si>
+    <t>砂糖</t>
+  </si>
+  <si>
+    <t>さとう</t>
+  </si>
+  <si>
+    <t>背</t>
+  </si>
+  <si>
+    <t>せ</t>
+  </si>
+  <si>
+    <t>背広</t>
+  </si>
+  <si>
+    <t>せびろ</t>
+  </si>
+  <si>
+    <t>セーター</t>
+  </si>
+  <si>
+    <t>生徒</t>
+  </si>
+  <si>
+    <t>せいと</t>
+  </si>
+  <si>
+    <t>石鹼</t>
+  </si>
+  <si>
+    <t>せっけん</t>
+  </si>
+  <si>
+    <t>狭い</t>
+  </si>
+  <si>
+    <t>せまい</t>
+  </si>
+  <si>
+    <t>千</t>
+  </si>
+  <si>
+    <t>せん</t>
+  </si>
+  <si>
+    <t>satou</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>sebiro</t>
+  </si>
+  <si>
+    <t>seetaa</t>
+  </si>
+  <si>
+    <t>seito</t>
+  </si>
+  <si>
+    <t>sekken</t>
+  </si>
+  <si>
+    <t>semai</t>
+  </si>
+  <si>
+    <t>sen</t>
+  </si>
+  <si>
+    <t>sugar</t>
+  </si>
+  <si>
+    <t>height; stature; back; spine</t>
+  </si>
+  <si>
+    <t>business suit</t>
+  </si>
+  <si>
+    <t>sweater; jumper</t>
+  </si>
+  <si>
+    <t>pupil; student</t>
+  </si>
+  <si>
+    <t>soap</t>
+  </si>
+  <si>
+    <t>narrow</t>
+  </si>
+  <si>
+    <t>1000; thousand</t>
+  </si>
+  <si>
+    <t>先月</t>
+  </si>
+  <si>
+    <t>せんげつ</t>
+  </si>
+  <si>
+    <t>先生</t>
+  </si>
+  <si>
+    <t>せんせい</t>
+  </si>
+  <si>
+    <t>先週</t>
+  </si>
+  <si>
+    <t>せんしゅう</t>
+  </si>
+  <si>
+    <t>洗濯</t>
+  </si>
+  <si>
+    <t>せんたく</t>
+  </si>
+  <si>
+    <t>写真</t>
+  </si>
+  <si>
+    <t>しゃしん</t>
+  </si>
+  <si>
+    <t>シャツ</t>
+  </si>
+  <si>
+    <t>シャワー</t>
+  </si>
+  <si>
+    <t>四</t>
+  </si>
+  <si>
+    <t>sengetsu</t>
+  </si>
+  <si>
+    <t>sensei</t>
+  </si>
+  <si>
+    <t>senshuu</t>
+  </si>
+  <si>
+    <t>sentaku</t>
+  </si>
+  <si>
+    <t>shashin</t>
+  </si>
+  <si>
+    <t>shatsu</t>
+  </si>
+  <si>
+    <t>shawaa</t>
+  </si>
+  <si>
+    <t>shi</t>
+  </si>
+  <si>
+    <t>last month</t>
+  </si>
+  <si>
+    <t>teacher; instructor; master</t>
+  </si>
+  <si>
+    <t>last week</t>
+  </si>
+  <si>
+    <t>washing; laundry</t>
+  </si>
+  <si>
+    <t>photograph; photo</t>
+  </si>
+  <si>
+    <t>shirt</t>
+  </si>
+  <si>
+    <t>shower</t>
+  </si>
+  <si>
+    <t>four; 4</t>
+  </si>
+  <si>
+    <t>七</t>
+  </si>
+  <si>
+    <t>しち</t>
+  </si>
+  <si>
+    <t>し</t>
+  </si>
+  <si>
+    <t>仕事</t>
+  </si>
+  <si>
+    <t>しごと</t>
+  </si>
+  <si>
+    <t>shichi</t>
+  </si>
+  <si>
+    <t>shigoto</t>
+  </si>
+  <si>
+    <t>work; job; business</t>
+  </si>
+  <si>
+    <t>閉まる</t>
+  </si>
+  <si>
+    <t>しまる</t>
+  </si>
+  <si>
+    <t>閉める</t>
+  </si>
+  <si>
+    <t>しめる</t>
+  </si>
+  <si>
+    <t>締める</t>
+  </si>
+  <si>
+    <t>新聞</t>
+  </si>
+  <si>
+    <t>しんぶん</t>
+  </si>
+  <si>
+    <t>死ぬ</t>
+  </si>
+  <si>
+    <t>しぬ</t>
+  </si>
+  <si>
+    <t>塩</t>
+  </si>
+  <si>
+    <t>しお</t>
+  </si>
+  <si>
+    <t>shimaru</t>
+  </si>
+  <si>
+    <t>shimeru</t>
+  </si>
+  <si>
+    <t>shinbun</t>
+  </si>
+  <si>
+    <t>shinu</t>
+  </si>
+  <si>
+    <t>shio</t>
+  </si>
+  <si>
+    <t>to close; to be closed</t>
+  </si>
+  <si>
+    <t>to close; to shut</t>
+  </si>
+  <si>
+    <t>to tie; to fasten; to tighten</t>
+  </si>
+  <si>
+    <t>newspaper</t>
+  </si>
+  <si>
+    <t>to die</t>
+  </si>
+  <si>
+    <t>salt</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>しろ</t>
+  </si>
+  <si>
+    <t>白い</t>
+  </si>
+  <si>
+    <t>しろい</t>
+  </si>
+  <si>
+    <t>知る</t>
+  </si>
+  <si>
+    <t>しる</t>
+  </si>
+  <si>
+    <t>下</t>
+  </si>
+  <si>
+    <t>した</t>
+  </si>
+  <si>
+    <t>質問</t>
+  </si>
+  <si>
+    <t>しつもん</t>
+  </si>
+  <si>
+    <t>静か</t>
+  </si>
+  <si>
+    <t>しずか</t>
+  </si>
+  <si>
+    <t>食堂</t>
+  </si>
+  <si>
+    <t>しょくどう</t>
+  </si>
+  <si>
+    <t>shiro</t>
+  </si>
+  <si>
+    <t>shiroi</t>
+  </si>
+  <si>
+    <t>shiru</t>
+  </si>
+  <si>
+    <t>shita</t>
+  </si>
+  <si>
+    <t>shitsumon</t>
+  </si>
+  <si>
+    <t>shizuka</t>
+  </si>
+  <si>
+    <t>shokudou</t>
+  </si>
+  <si>
+    <t>white; innocence; innocent person</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>to know</t>
+  </si>
+  <si>
+    <t>below; down; under; bottom</t>
+  </si>
+  <si>
+    <t>question; inquiry</t>
+  </si>
+  <si>
+    <t>quiet</t>
+  </si>
+  <si>
+    <t>cafetaria; dining room</t>
+  </si>
+  <si>
+    <t>醬油</t>
+  </si>
+  <si>
+    <t>しょうゆ</t>
+  </si>
+  <si>
+    <t>宿題</t>
+  </si>
+  <si>
+    <t>しゅくだい</t>
+  </si>
+  <si>
+    <t>そば</t>
+  </si>
+  <si>
+    <t>そっち</t>
+  </si>
+  <si>
+    <t>そちら</t>
+  </si>
+  <si>
+    <t>そこ</t>
+  </si>
+  <si>
+    <t>空</t>
+  </si>
+  <si>
+    <t>そら</t>
+  </si>
+  <si>
+    <t>それ</t>
+  </si>
+  <si>
+    <t>それでは</t>
+  </si>
+  <si>
+    <t>shouyu</t>
+  </si>
+  <si>
+    <t>shukudai</t>
+  </si>
+  <si>
+    <t>soba</t>
+  </si>
+  <si>
+    <t>socchi</t>
+  </si>
+  <si>
+    <t>sochira</t>
+  </si>
+  <si>
+    <t>soko</t>
+  </si>
+  <si>
+    <t>sora</t>
+  </si>
+  <si>
+    <t>sore</t>
+  </si>
+  <si>
+    <t>sore dewa</t>
+  </si>
+  <si>
+    <t>sono</t>
+  </si>
+  <si>
+    <t>その</t>
+  </si>
+  <si>
+    <t>soy sauce</t>
+  </si>
+  <si>
+    <t>homework; assignment; pending issue</t>
+  </si>
+  <si>
+    <t>near; beside</t>
+  </si>
+  <si>
+    <t>that way; over there</t>
+  </si>
+  <si>
+    <t>that way (distant from speaker; close to listener); you; your family</t>
+  </si>
+  <si>
+    <t>that place; there</t>
+  </si>
+  <si>
+    <t>sky; the air</t>
+  </si>
+  <si>
+    <t>in that situation</t>
+  </si>
+  <si>
+    <t>外</t>
+  </si>
+  <si>
+    <t>そと</t>
+  </si>
+  <si>
+    <t>掃除</t>
+  </si>
+  <si>
+    <t>そうじ</t>
+  </si>
+  <si>
+    <t>直ぐに</t>
+  </si>
+  <si>
+    <t>すぐに</t>
+  </si>
+  <si>
+    <t>水曜日</t>
+  </si>
+  <si>
+    <t>すいようび</t>
+  </si>
+  <si>
+    <t>スカート</t>
+  </si>
+  <si>
+    <t>好き</t>
+  </si>
+  <si>
+    <t>すき</t>
+  </si>
+  <si>
+    <t>少し</t>
+  </si>
+  <si>
+    <t>すこし</t>
+  </si>
+  <si>
+    <t>少ない</t>
+  </si>
+  <si>
+    <t>すくない</t>
+  </si>
+  <si>
+    <t>soto</t>
+  </si>
+  <si>
+    <t>souji</t>
+  </si>
+  <si>
+    <t>sugu ni</t>
+  </si>
+  <si>
+    <t>suiyoubi</t>
+  </si>
+  <si>
+    <t>sukaato</t>
+  </si>
+  <si>
+    <t>suki</t>
+  </si>
+  <si>
+    <t>sukoshi</t>
+  </si>
+  <si>
+    <t>sukunai</t>
+  </si>
+  <si>
+    <t>outside; exterior</t>
+  </si>
+  <si>
+    <t>to clean; to sweep</t>
+  </si>
+  <si>
+    <t>immediately; right away; instantly</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>skirt</t>
+  </si>
+  <si>
+    <t>like</t>
+  </si>
+  <si>
+    <t>a little (bit); small quantity; few; short distance</t>
+  </si>
+  <si>
+    <t>few; a little; scarce; insufficient; seldom</t>
+  </si>
+  <si>
+    <t>住む</t>
+  </si>
+  <si>
+    <t>すむ</t>
+  </si>
+  <si>
+    <t>スポーツ</t>
+  </si>
+  <si>
+    <t>スプーン</t>
+  </si>
+  <si>
+    <t>スリッパ</t>
+  </si>
+  <si>
+    <t>ストーブ</t>
+  </si>
+  <si>
+    <t>吸う</t>
+  </si>
+  <si>
+    <t>すう</t>
+  </si>
+  <si>
+    <t>座る</t>
+  </si>
+  <si>
+    <t>すわる</t>
+  </si>
+  <si>
+    <t>sumu</t>
+  </si>
+  <si>
+    <t>supootsu</t>
+  </si>
+  <si>
+    <t>supuun</t>
+  </si>
+  <si>
+    <t>surippa</t>
+  </si>
+  <si>
+    <t>sutoobu</t>
+  </si>
+  <si>
+    <t>suu</t>
+  </si>
+  <si>
+    <t>suwaru</t>
+  </si>
+  <si>
+    <t>to live in; to reside; to inhabit; to dwell; to abide</t>
+  </si>
+  <si>
+    <t>sport; sports</t>
+  </si>
+  <si>
+    <t>spoon</t>
+  </si>
+  <si>
+    <t>slipper; slippers</t>
+  </si>
+  <si>
+    <t>heater; stove</t>
+  </si>
+  <si>
+    <t>to smoke; to suck</t>
+  </si>
+  <si>
+    <t>to sit</t>
+  </si>
+  <si>
+    <t>涼しい</t>
+  </si>
+  <si>
+    <t>すずしい</t>
+  </si>
+  <si>
+    <t>たばこ</t>
+  </si>
+  <si>
+    <t>食べ物</t>
+  </si>
+  <si>
+    <t>たべもの</t>
+  </si>
+  <si>
+    <t>食べる</t>
+  </si>
+  <si>
+    <t>たべる</t>
+  </si>
+  <si>
+    <t>多分</t>
+  </si>
+  <si>
+    <t>たぶん</t>
+  </si>
+  <si>
+    <t>大変</t>
+  </si>
+  <si>
+    <t>たいへん</t>
+  </si>
+  <si>
+    <t>大切</t>
+  </si>
+  <si>
+    <t>たいせつ</t>
+  </si>
+  <si>
+    <t>suzushii</t>
+  </si>
+  <si>
+    <t>tabako</t>
+  </si>
+  <si>
+    <t>tabemono</t>
+  </si>
+  <si>
+    <t>taberu</t>
+  </si>
+  <si>
+    <t>tabun</t>
+  </si>
+  <si>
+    <t>taihen</t>
+  </si>
+  <si>
+    <t>taisetsu</t>
+  </si>
+  <si>
+    <t>refreshing; cool</t>
+  </si>
+  <si>
+    <t>tobacco; cigarette</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>to eat</t>
+  </si>
+  <si>
+    <t>perhaps; probably</t>
+  </si>
+  <si>
+    <t>very; greatly; terribly; serious; difficult</t>
+  </si>
+  <si>
+    <t>important; necessary; indispensable; beloved</t>
+  </si>
+  <si>
+    <t>大使館</t>
+  </si>
+  <si>
+    <t>たいしかん</t>
+  </si>
+  <si>
+    <t>高い</t>
+  </si>
+  <si>
+    <t>たかい</t>
+  </si>
+  <si>
+    <t>沢山</t>
+  </si>
+  <si>
+    <t>たくさん</t>
+  </si>
+  <si>
+    <t>タクシー</t>
+  </si>
+  <si>
+    <t>卵</t>
+  </si>
+  <si>
+    <t>たまご</t>
+  </si>
+  <si>
+    <t>誕生日</t>
+  </si>
+  <si>
+    <t>たんじょうび</t>
+  </si>
+  <si>
+    <t>頼む</t>
+  </si>
+  <si>
+    <t>たのむ</t>
+  </si>
+  <si>
+    <t>taishikan</t>
+  </si>
+  <si>
+    <t>takai</t>
+  </si>
+  <si>
+    <t>takusan</t>
+  </si>
+  <si>
+    <t>takushii</t>
+  </si>
+  <si>
+    <t>tamago</t>
+  </si>
+  <si>
+    <t>tanjoubi</t>
+  </si>
+  <si>
+    <t>tanomu</t>
+  </si>
+  <si>
+    <t>noun, adverbial noun, adjective, na-adjective</t>
+  </si>
+  <si>
+    <t>embassy</t>
+  </si>
+  <si>
+    <t>high; tall; expensive; above average</t>
+  </si>
+  <si>
+    <t>many</t>
+  </si>
+  <si>
+    <t>taxi</t>
+  </si>
+  <si>
+    <t>eggs; egg</t>
+  </si>
+  <si>
+    <t>birthday</t>
+  </si>
+  <si>
+    <t>to ask</t>
+  </si>
+  <si>
+    <t>楽しい</t>
+  </si>
+  <si>
+    <t>たのしい</t>
+  </si>
+  <si>
+    <t>縦</t>
+  </si>
+  <si>
+    <t>たて</t>
+  </si>
+  <si>
+    <t>建物</t>
+  </si>
+  <si>
+    <t>たてもの</t>
+  </si>
+  <si>
+    <t>立つ</t>
+  </si>
+  <si>
+    <t>たつ</t>
+  </si>
+  <si>
+    <t>手</t>
+  </si>
+  <si>
+    <t>て</t>
+  </si>
+  <si>
+    <t>テーブル</t>
+  </si>
+  <si>
+    <t>テープ</t>
+  </si>
+  <si>
+    <t>テープレコーダー</t>
+  </si>
+  <si>
+    <t>tanoshii</t>
+  </si>
+  <si>
+    <t>tate</t>
+  </si>
+  <si>
+    <t>tatemono</t>
+  </si>
+  <si>
+    <t>tatsu</t>
+  </si>
+  <si>
+    <t>te</t>
+  </si>
+  <si>
+    <t>teeburu</t>
+  </si>
+  <si>
+    <t>teepu</t>
+  </si>
+  <si>
+    <t>teepu rekoodaa</t>
+  </si>
+  <si>
+    <t>enjoyable; fun</t>
+  </si>
+  <si>
+    <t>length; height</t>
+  </si>
+  <si>
+    <t>building</t>
+  </si>
+  <si>
+    <t>to stand; to stand up</t>
+  </si>
+  <si>
+    <t>hand; arm</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>tape</t>
+  </si>
+  <si>
+    <t>tape recorder</t>
+  </si>
+  <si>
+    <t>手紙</t>
+  </si>
+  <si>
+    <t>てがみ</t>
+  </si>
+  <si>
+    <t>天気</t>
+  </si>
+  <si>
+    <t>てんき</t>
+  </si>
+  <si>
+    <t>テレビ</t>
+  </si>
+  <si>
+    <t>テスト</t>
+  </si>
+  <si>
+    <t>戸</t>
+  </si>
+  <si>
+    <t>と</t>
+  </si>
+  <si>
+    <t>飛ぶ</t>
+  </si>
+  <si>
+    <t>とぶ</t>
+  </si>
+  <si>
+    <t>トイレ</t>
+  </si>
+  <si>
+    <t>時計</t>
+  </si>
+  <si>
+    <t>とけい</t>
+  </si>
+  <si>
+    <t>tegami</t>
+  </si>
+  <si>
+    <t>tenki</t>
+  </si>
+  <si>
+    <t>terebi</t>
+  </si>
+  <si>
+    <t>tesuto</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>tobu</t>
+  </si>
+  <si>
+    <t>toire</t>
+  </si>
+  <si>
+    <t>tokei</t>
+  </si>
+  <si>
+    <t>letter (message)</t>
+  </si>
+  <si>
+    <t>weather; the elements</t>
+  </si>
+  <si>
+    <t>television; TV</t>
+  </si>
+  <si>
+    <t>examination; quiz; test</t>
+  </si>
+  <si>
+    <t>Japanese style door</t>
+  </si>
+  <si>
+    <t>to fly; to hop</t>
+  </si>
+  <si>
+    <t>toilet</t>
+  </si>
+  <si>
+    <t>watch; clock; timepiece</t>
+  </si>
+  <si>
+    <t>時</t>
+  </si>
+  <si>
+    <t>とき</t>
+  </si>
+  <si>
+    <t>時々</t>
+  </si>
+  <si>
+    <t>ときどき</t>
+  </si>
+  <si>
+    <t>所</t>
+  </si>
+  <si>
+    <t>ところ</t>
+  </si>
+  <si>
+    <t>止まる</t>
+  </si>
+  <si>
+    <t>とまる</t>
+  </si>
+  <si>
+    <t>友達</t>
+  </si>
+  <si>
+    <t>ともだち</t>
+  </si>
+  <si>
+    <t>隣</t>
+  </si>
+  <si>
+    <t>となり</t>
+  </si>
+  <si>
+    <t>遠い</t>
+  </si>
+  <si>
+    <t>とおい</t>
+  </si>
+  <si>
+    <t>toki</t>
+  </si>
+  <si>
+    <t>tokidoki</t>
+  </si>
+  <si>
+    <t>tokoro</t>
+  </si>
+  <si>
+    <t>tomaru</t>
+  </si>
+  <si>
+    <t>tomodachi</t>
+  </si>
+  <si>
+    <t>tonari</t>
+  </si>
+  <si>
+    <t>tooi</t>
+  </si>
+  <si>
+    <t>time; moment; occasion; chance</t>
+  </si>
+  <si>
+    <t>sometimes; at times</t>
+  </si>
+  <si>
+    <t>place</t>
+  </si>
+  <si>
+    <t>to stop; to come to a halt</t>
+  </si>
+  <si>
+    <t>friend; companion</t>
+  </si>
+  <si>
+    <t>next door to</t>
+  </si>
+  <si>
+    <t>far</t>
+  </si>
+  <si>
+    <t>十日</t>
+  </si>
+  <si>
+    <t>とおか</t>
+  </si>
+  <si>
+    <t>鳥</t>
+  </si>
+  <si>
+    <t>とり</t>
+  </si>
+  <si>
+    <t>鶏肉</t>
+  </si>
+  <si>
+    <t>とりにく</t>
+  </si>
+  <si>
+    <t>取る</t>
+  </si>
+  <si>
+    <t>とる</t>
+  </si>
+  <si>
+    <t>撮る</t>
+  </si>
+  <si>
+    <t>年</t>
+  </si>
+  <si>
+    <t>とし</t>
+  </si>
+  <si>
+    <t>図書館</t>
+  </si>
+  <si>
+    <t>としょかん</t>
+  </si>
+  <si>
+    <t>tooka</t>
+  </si>
+  <si>
+    <t>tori</t>
+  </si>
+  <si>
+    <t>toriniku</t>
+  </si>
+  <si>
+    <t>toru</t>
+  </si>
+  <si>
+    <t>toshi</t>
+  </si>
+  <si>
+    <t>toshokan</t>
+  </si>
+  <si>
+    <t>tenth day of the month; 10 days</t>
+  </si>
+  <si>
+    <t>bird</t>
+  </si>
+  <si>
+    <t>chicken meat</t>
+  </si>
+  <si>
+    <t>to take; to pick up; to harvest; to earn; to win; to choose</t>
+  </si>
+  <si>
+    <t>to take a photo or record a film</t>
+  </si>
+  <si>
+    <t>year; age</t>
+  </si>
+  <si>
+    <t>library</t>
+  </si>
+  <si>
+    <t>次</t>
+  </si>
+  <si>
+    <t>つぎ</t>
+  </si>
+  <si>
+    <t>ついたち</t>
+  </si>
+  <si>
+    <t>疲れる</t>
+  </si>
+  <si>
+    <t>つかれる</t>
+  </si>
+  <si>
+    <t>使う</t>
+  </si>
+  <si>
+    <t>つかう</t>
+  </si>
+  <si>
+    <t>つける</t>
+  </si>
+  <si>
+    <t>付ける</t>
+  </si>
+  <si>
+    <t>tsugi</t>
+  </si>
+  <si>
+    <t>tsuitachi</t>
+  </si>
+  <si>
+    <t>tsukareru</t>
+  </si>
+  <si>
+    <t>tsukau</t>
+  </si>
+  <si>
+    <t>tsukeru</t>
+  </si>
+  <si>
+    <t>next</t>
+  </si>
+  <si>
+    <t>first day of the month</t>
+  </si>
+  <si>
+    <t>to get tired</t>
+  </si>
+  <si>
+    <t>to use</t>
+  </si>
+  <si>
+    <t>to turn on</t>
+  </si>
+  <si>
+    <t>to attach; affix; add; apply</t>
+  </si>
+  <si>
+    <t>着く</t>
+  </si>
+  <si>
+    <t>つく</t>
+  </si>
+  <si>
+    <t>机</t>
+  </si>
+  <si>
+    <t>つくえ</t>
+  </si>
+  <si>
+    <t>作る</t>
+  </si>
+  <si>
+    <t>つくる</t>
+  </si>
+  <si>
+    <t>詰まらない</t>
+  </si>
+  <si>
+    <t>つまらない</t>
+  </si>
+  <si>
+    <t>冷たい</t>
+  </si>
+  <si>
+    <t>つめたい</t>
+  </si>
+  <si>
+    <t>勤める</t>
+  </si>
+  <si>
+    <t>つとめる</t>
+  </si>
+  <si>
+    <t>強い</t>
+  </si>
+  <si>
+    <t>つよい</t>
+  </si>
+  <si>
+    <t>tsuku</t>
+  </si>
+  <si>
+    <t>tsukue</t>
+  </si>
+  <si>
+    <t>tsukuru</t>
+  </si>
+  <si>
+    <t>tsumaranai</t>
+  </si>
+  <si>
+    <t>tsumetai</t>
+  </si>
+  <si>
+    <t>tsutomeru</t>
+  </si>
+  <si>
+    <t>tsuyoi</t>
+  </si>
+  <si>
+    <t>to arrive at</t>
+  </si>
+  <si>
+    <t>desk</t>
+  </si>
+  <si>
+    <t>to make</t>
+  </si>
+  <si>
+    <t>boring</t>
+  </si>
+  <si>
+    <t>cold to the touch</t>
+  </si>
+  <si>
+    <t>to work for someone</t>
+  </si>
+  <si>
+    <t>powerful</t>
+  </si>
+  <si>
+    <t>上</t>
+  </si>
+  <si>
+    <t>うえ</t>
+  </si>
+  <si>
+    <t>生まれる</t>
+  </si>
+  <si>
+    <t>うまれる</t>
+  </si>
+  <si>
+    <t>海</t>
+  </si>
+  <si>
+    <t>うみ</t>
+  </si>
+  <si>
+    <t>売る</t>
+  </si>
+  <si>
+    <t>うる</t>
+  </si>
+  <si>
+    <t>煩い</t>
+  </si>
+  <si>
+    <t>うるさい</t>
+  </si>
+  <si>
+    <t>ue</t>
+  </si>
+  <si>
+    <t>umareru</t>
+  </si>
+  <si>
+    <t>umi</t>
+  </si>
+  <si>
+    <t>uru</t>
+  </si>
+  <si>
+    <t>urusai</t>
+  </si>
+  <si>
+    <t>above; up; over; top; surface</t>
+  </si>
+  <si>
+    <t>to be born</t>
+  </si>
+  <si>
+    <t>sea</t>
+  </si>
+  <si>
+    <t>to sell</t>
+  </si>
+  <si>
+    <t>noisy; annoying</t>
+  </si>
+  <si>
+    <t>後ろ</t>
+  </si>
+  <si>
+    <t>薄い</t>
+  </si>
+  <si>
+    <t>うしろ</t>
+  </si>
+  <si>
+    <t>うすい</t>
+  </si>
+  <si>
+    <t>歌</t>
+  </si>
+  <si>
+    <t>うた</t>
+  </si>
+  <si>
+    <t>歌う</t>
+  </si>
+  <si>
+    <t>うたう</t>
+  </si>
+  <si>
+    <t>上着</t>
+  </si>
+  <si>
+    <t>うわぎ</t>
+  </si>
+  <si>
+    <t>ushiro</t>
+  </si>
+  <si>
+    <t>usui</t>
+  </si>
+  <si>
+    <t>uta</t>
+  </si>
+  <si>
+    <t>utau</t>
+  </si>
+  <si>
+    <t>uwagi</t>
+  </si>
+  <si>
+    <t>back; behind; rear</t>
+  </si>
+  <si>
+    <t>thin; weak</t>
+  </si>
+  <si>
+    <t>song</t>
+  </si>
+  <si>
+    <t>to sing</t>
+  </si>
+  <si>
+    <t>coat; tunic; jacket; outer garment</t>
+  </si>
+  <si>
+    <t>ワイシャツ</t>
+  </si>
+  <si>
+    <t>若い</t>
+  </si>
+  <si>
+    <t>わかい</t>
+  </si>
+  <si>
+    <t>分かる</t>
+  </si>
+  <si>
+    <t>わかる</t>
+  </si>
+  <si>
+    <t>わすれる</t>
+  </si>
+  <si>
+    <t>忘れる</t>
+  </si>
+  <si>
+    <t>渡る</t>
+  </si>
+  <si>
+    <t>わたる</t>
+  </si>
+  <si>
+    <t>wai shatsu</t>
+  </si>
+  <si>
+    <t>wakai</t>
+  </si>
+  <si>
+    <t>wakaru</t>
+  </si>
+  <si>
+    <t>warui</t>
+  </si>
+  <si>
+    <t>wasureru</t>
+  </si>
+  <si>
+    <t>noun, katakana, wasei</t>
+  </si>
+  <si>
+    <t>wataru</t>
+  </si>
+  <si>
+    <t>young</t>
+  </si>
+  <si>
+    <t>to understand; to comprehend; to grasp; to see; to get; to follow</t>
+  </si>
+  <si>
+    <t>bad; poor; undesirable</t>
+  </si>
+  <si>
+    <t>to forget</t>
+  </si>
+  <si>
+    <t>to go across</t>
+  </si>
+  <si>
+    <t>悪い</t>
+  </si>
+  <si>
+    <t>わるい</t>
+  </si>
+  <si>
+    <t>私</t>
+  </si>
+  <si>
+    <t>わたし</t>
+  </si>
+  <si>
+    <t>渡す</t>
+  </si>
+  <si>
+    <t>わたす</t>
+  </si>
+  <si>
+    <t>山</t>
+  </si>
+  <si>
+    <t>やま</t>
+  </si>
+  <si>
+    <t>八百屋</t>
+  </si>
+  <si>
+    <t>やおや</t>
+  </si>
+  <si>
+    <t>やる</t>
+  </si>
+  <si>
+    <t>野菜</t>
+  </si>
+  <si>
+    <t>やさい</t>
+  </si>
+  <si>
+    <t>易しい</t>
+  </si>
+  <si>
+    <t>やさしい</t>
+  </si>
+  <si>
+    <t>watashi</t>
+  </si>
+  <si>
+    <t>watasu</t>
+  </si>
+  <si>
+    <t>yama</t>
+  </si>
+  <si>
+    <t>yaoya</t>
+  </si>
+  <si>
+    <t>yaru</t>
+  </si>
+  <si>
+    <t>yasai</t>
+  </si>
+  <si>
+    <t>yasashii</t>
+  </si>
+  <si>
+    <t>I; myself</t>
+  </si>
+  <si>
+    <t>to hand over</t>
+  </si>
+  <si>
+    <t>mountain; hill</t>
+  </si>
+  <si>
+    <t>greengrocer; fruit and vegetable shop; versatile</t>
+  </si>
+  <si>
+    <t>to do</t>
+  </si>
+  <si>
+    <t>vegetable</t>
+  </si>
+  <si>
+    <t>easy; simple</t>
+  </si>
+  <si>
+    <t>安い</t>
+  </si>
+  <si>
+    <t>やすい</t>
+  </si>
+  <si>
+    <t>休み</t>
+  </si>
+  <si>
+    <t>やすみ</t>
+  </si>
+  <si>
+    <t>休む</t>
+  </si>
+  <si>
+    <t>やすむ</t>
+  </si>
+  <si>
+    <t>八つ</t>
+  </si>
+  <si>
+    <t>やっつ</t>
+  </si>
+  <si>
+    <t>呼ぶ</t>
+  </si>
+  <si>
+    <t>よぶ</t>
+  </si>
+  <si>
+    <t>良い</t>
+  </si>
+  <si>
+    <t>よい・いい</t>
+  </si>
+  <si>
+    <t>よっか</t>
+  </si>
+  <si>
+    <t>四日</t>
+  </si>
+  <si>
+    <t>yasui</t>
+  </si>
+  <si>
+    <t>yasumi</t>
+  </si>
+  <si>
+    <t>yasumu</t>
+  </si>
+  <si>
+    <t>yattsu</t>
+  </si>
+  <si>
+    <t>yobu</t>
+  </si>
+  <si>
+    <t>yoi/ii</t>
+  </si>
+  <si>
+    <t>yokka</t>
+  </si>
+  <si>
+    <t>cheap; inexpensive</t>
+  </si>
+  <si>
+    <t>rest; vacation; holiday</t>
+  </si>
+  <si>
+    <t>to be absent; to take a day off; to rest</t>
+  </si>
+  <si>
+    <t>to call out; to invite</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>fourth day of the month; 4 days</t>
+  </si>
+  <si>
+    <t>横</t>
+  </si>
+  <si>
+    <t>よこ</t>
+  </si>
+  <si>
+    <t>よく</t>
+  </si>
+  <si>
+    <t>読む</t>
+  </si>
+  <si>
+    <t>よむ</t>
+  </si>
+  <si>
+    <t>夜</t>
+  </si>
+  <si>
+    <t>よる</t>
+  </si>
+  <si>
+    <t>四つ</t>
+  </si>
+  <si>
+    <t>よつ</t>
+  </si>
+  <si>
+    <t>洋服</t>
+  </si>
+  <si>
+    <t>ようふく</t>
+  </si>
+  <si>
+    <t>八日</t>
+  </si>
+  <si>
+    <t>ようか</t>
+  </si>
+  <si>
+    <t>yoko</t>
+  </si>
+  <si>
+    <t>yoku</t>
+  </si>
+  <si>
+    <t>yomu</t>
+  </si>
+  <si>
+    <t>yoru</t>
+  </si>
+  <si>
+    <t>yotsu</t>
+  </si>
+  <si>
+    <t>youfuku</t>
+  </si>
+  <si>
+    <t>youka</t>
+  </si>
+  <si>
+    <t>beside; side; width</t>
+  </si>
+  <si>
+    <t>often; well</t>
+  </si>
+  <si>
+    <t>to read; to guess; to predict; to read (someone's thoughts)</t>
+  </si>
+  <si>
+    <t>evening; night</t>
+  </si>
+  <si>
+    <t>western clothes</t>
+  </si>
+  <si>
+    <t>eight day of the month; 8 days</t>
+  </si>
+  <si>
+    <t>雪</t>
+  </si>
+  <si>
+    <t>ゆき</t>
+  </si>
+  <si>
+    <t>ゆっくり</t>
+  </si>
+  <si>
+    <t>昨夜</t>
+  </si>
+  <si>
+    <t>ゆうべ</t>
+  </si>
+  <si>
+    <t>弱い</t>
+  </si>
+  <si>
+    <t>よわい</t>
+  </si>
+  <si>
+    <t>郵便局</t>
+  </si>
+  <si>
+    <t>ゆうびんきょく</t>
+  </si>
+  <si>
+    <t>夕方</t>
+  </si>
+  <si>
+    <t>ゆうがた</t>
+  </si>
+  <si>
+    <t>夕飯</t>
+  </si>
+  <si>
+    <t>ゆうはん</t>
+  </si>
+  <si>
+    <t>yowai</t>
+  </si>
+  <si>
+    <t>yuki</t>
+  </si>
+  <si>
+    <t>yukkuri</t>
+  </si>
+  <si>
+    <t>yuube</t>
+  </si>
+  <si>
+    <t>yuubinkyoku</t>
+  </si>
+  <si>
+    <t>yuugata</t>
+  </si>
+  <si>
+    <t>yuuhan</t>
+  </si>
+  <si>
+    <t>weak</t>
+  </si>
+  <si>
+    <t>snow</t>
+  </si>
+  <si>
+    <t>slowly</t>
+  </si>
+  <si>
+    <t>last night</t>
+  </si>
+  <si>
+    <t>post office</t>
+  </si>
+  <si>
+    <t>evening; dusk</t>
+  </si>
+  <si>
+    <t>evening meal</t>
+  </si>
+  <si>
+    <t>有名</t>
+  </si>
+  <si>
+    <t>ゆうめい</t>
+  </si>
+  <si>
+    <t>雑誌</t>
+  </si>
+  <si>
+    <t>ざっし</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>ぜんぶ</t>
+  </si>
+  <si>
+    <t>ゼロ</t>
+  </si>
+  <si>
+    <t>ズボン</t>
+  </si>
+  <si>
+    <t>yuumei</t>
+  </si>
+  <si>
+    <t>zasshi</t>
+  </si>
+  <si>
+    <t>zenbu</t>
+  </si>
+  <si>
+    <t>zubon</t>
+  </si>
+  <si>
+    <t>famous</t>
+  </si>
+  <si>
+    <t>magazine</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>trousers; pants</t>
   </si>
 </sst>
 </file>
@@ -4993,7 +7753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06195E36-B216-40D7-A65F-59D0663B1FBE}">
-  <dimension ref="A1:G401"/>
+  <dimension ref="A1:G645"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -14227,6 +16987,5618 @@
         <v>1536</v>
       </c>
     </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402" t="s">
+        <v>5</v>
+      </c>
+      <c r="C402" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D402" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E402" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F402" t="s">
+        <v>113</v>
+      </c>
+      <c r="G402" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403" t="s">
+        <v>5</v>
+      </c>
+      <c r="C403" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D403" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E403" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F403" t="s">
+        <v>62</v>
+      </c>
+      <c r="G403" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404" t="s">
+        <v>5</v>
+      </c>
+      <c r="C404" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D404" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E404" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F404" t="s">
+        <v>112</v>
+      </c>
+      <c r="G404" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405" t="s">
+        <v>5</v>
+      </c>
+      <c r="C405" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D405" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E405" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F405" t="s">
+        <v>64</v>
+      </c>
+      <c r="G405" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406" t="s">
+        <v>5</v>
+      </c>
+      <c r="C406" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D406" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E406" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F406" t="s">
+        <v>64</v>
+      </c>
+      <c r="G406" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A407">
+        <v>406</v>
+      </c>
+      <c r="B407" t="s">
+        <v>5</v>
+      </c>
+      <c r="C407" t="s">
+        <v>1545</v>
+      </c>
+      <c r="D407" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E407" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F407" t="s">
+        <v>64</v>
+      </c>
+      <c r="G407" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408" t="s">
+        <v>5</v>
+      </c>
+      <c r="C408" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D408" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E408" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F408" t="s">
+        <v>61</v>
+      </c>
+      <c r="G408" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409" t="s">
+        <v>5</v>
+      </c>
+      <c r="C409" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D409" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E409" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F409" t="s">
+        <v>64</v>
+      </c>
+      <c r="G409" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A410">
+        <v>409</v>
+      </c>
+      <c r="B410" t="s">
+        <v>5</v>
+      </c>
+      <c r="C410" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D410" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E410" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F410" t="s">
+        <v>64</v>
+      </c>
+      <c r="G410" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A411">
+        <v>410</v>
+      </c>
+      <c r="B411" t="s">
+        <v>5</v>
+      </c>
+      <c r="C411" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D411" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E411" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F411" t="s">
+        <v>270</v>
+      </c>
+      <c r="G411" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A412">
+        <v>411</v>
+      </c>
+      <c r="B412" t="s">
+        <v>5</v>
+      </c>
+      <c r="C412" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D412" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E412" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F412" t="s">
+        <v>64</v>
+      </c>
+      <c r="G412" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A413">
+        <v>412</v>
+      </c>
+      <c r="B413" t="s">
+        <v>5</v>
+      </c>
+      <c r="C413" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D413" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E413" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F413" t="s">
+        <v>64</v>
+      </c>
+      <c r="G413" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A414">
+        <v>413</v>
+      </c>
+      <c r="B414" t="s">
+        <v>5</v>
+      </c>
+      <c r="C414" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D414" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E414" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F414" t="s">
+        <v>64</v>
+      </c>
+      <c r="G414" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A415">
+        <v>414</v>
+      </c>
+      <c r="B415" t="s">
+        <v>5</v>
+      </c>
+      <c r="C415" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D415" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E415" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F415" t="s">
+        <v>64</v>
+      </c>
+      <c r="G415" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A416">
+        <v>415</v>
+      </c>
+      <c r="B416" t="s">
+        <v>5</v>
+      </c>
+      <c r="C416" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D416" t="s">
+        <v>1571</v>
+      </c>
+      <c r="E416" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F416" t="s">
+        <v>1595</v>
+      </c>
+      <c r="G416" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A417">
+        <v>416</v>
+      </c>
+      <c r="B417" t="s">
+        <v>5</v>
+      </c>
+      <c r="C417" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D417" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E417" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F417" t="s">
+        <v>113</v>
+      </c>
+      <c r="G417" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A418">
+        <v>417</v>
+      </c>
+      <c r="B418" t="s">
+        <v>5</v>
+      </c>
+      <c r="C418" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D418" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E418" t="s">
+        <v>1611</v>
+      </c>
+      <c r="F418" t="s">
+        <v>64</v>
+      </c>
+      <c r="G418" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A419">
+        <v>418</v>
+      </c>
+      <c r="B419" t="s">
+        <v>5</v>
+      </c>
+      <c r="C419" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D419" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E419" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F419" t="s">
+        <v>64</v>
+      </c>
+      <c r="G419" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A420">
+        <v>419</v>
+      </c>
+      <c r="B420" t="s">
+        <v>5</v>
+      </c>
+      <c r="C420" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D420" t="s">
+        <v>1602</v>
+      </c>
+      <c r="E420" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F420" t="s">
+        <v>270</v>
+      </c>
+      <c r="G420" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A421">
+        <v>420</v>
+      </c>
+      <c r="B421" t="s">
+        <v>5</v>
+      </c>
+      <c r="C421" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D421" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E421" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F421" t="s">
+        <v>62</v>
+      </c>
+      <c r="G421" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A422">
+        <v>421</v>
+      </c>
+      <c r="B422" t="s">
+        <v>5</v>
+      </c>
+      <c r="C422" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D422" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E422" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F422" t="s">
+        <v>666</v>
+      </c>
+      <c r="G422" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A423">
+        <v>422</v>
+      </c>
+      <c r="B423" t="s">
+        <v>5</v>
+      </c>
+      <c r="C423" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D423" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E423" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F423" t="s">
+        <v>64</v>
+      </c>
+      <c r="G423" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A424">
+        <v>423</v>
+      </c>
+      <c r="B424" t="s">
+        <v>5</v>
+      </c>
+      <c r="C424" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D424" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E424" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F424" t="s">
+        <v>64</v>
+      </c>
+      <c r="G424" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A425">
+        <v>424</v>
+      </c>
+      <c r="B425" t="s">
+        <v>5</v>
+      </c>
+      <c r="C425" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D425" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E425" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F425" t="s">
+        <v>64</v>
+      </c>
+      <c r="G425" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A426">
+        <v>425</v>
+      </c>
+      <c r="B426" t="s">
+        <v>5</v>
+      </c>
+      <c r="C426" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D426" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E426" t="s">
+        <v>1641</v>
+      </c>
+      <c r="F426" t="s">
+        <v>64</v>
+      </c>
+      <c r="G426" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A427">
+        <v>426</v>
+      </c>
+      <c r="B427" t="s">
+        <v>5</v>
+      </c>
+      <c r="C427" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D427" t="s">
+        <v>1643</v>
+      </c>
+      <c r="E427" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F427" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G427" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A428">
+        <v>427</v>
+      </c>
+      <c r="B428" t="s">
+        <v>5</v>
+      </c>
+      <c r="C428" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D428" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E428" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F428" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G428" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A429">
+        <v>428</v>
+      </c>
+      <c r="B429" t="s">
+        <v>5</v>
+      </c>
+      <c r="C429" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D429" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E429" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F429" t="s">
+        <v>62</v>
+      </c>
+      <c r="G429" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A430">
+        <v>429</v>
+      </c>
+      <c r="B430" t="s">
+        <v>5</v>
+      </c>
+      <c r="C430" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D430" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E430" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F430" t="s">
+        <v>62</v>
+      </c>
+      <c r="G430" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A431">
+        <v>430</v>
+      </c>
+      <c r="B431" t="s">
+        <v>5</v>
+      </c>
+      <c r="C431" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D431" t="s">
+        <v>1637</v>
+      </c>
+      <c r="E431" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F431" t="s">
+        <v>65</v>
+      </c>
+      <c r="G431" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A432">
+        <v>431</v>
+      </c>
+      <c r="B432" t="s">
+        <v>5</v>
+      </c>
+      <c r="C432" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D432" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E432" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F432" t="s">
+        <v>64</v>
+      </c>
+      <c r="G432" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A433">
+        <v>432</v>
+      </c>
+      <c r="B433" t="s">
+        <v>5</v>
+      </c>
+      <c r="C433" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D433" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E433" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F433" t="s">
+        <v>309</v>
+      </c>
+      <c r="G433" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A434">
+        <v>433</v>
+      </c>
+      <c r="B434" t="s">
+        <v>5</v>
+      </c>
+      <c r="C434" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D434" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E434" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F434" t="s">
+        <v>64</v>
+      </c>
+      <c r="G434" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A435">
+        <v>434</v>
+      </c>
+      <c r="B435" t="s">
+        <v>5</v>
+      </c>
+      <c r="C435" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D435" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E435" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F435" t="s">
+        <v>64</v>
+      </c>
+      <c r="G435" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A436">
+        <v>435</v>
+      </c>
+      <c r="B436" t="s">
+        <v>5</v>
+      </c>
+      <c r="C436" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D436" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E436" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F436" t="s">
+        <v>61</v>
+      </c>
+      <c r="G436" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A437">
+        <v>436</v>
+      </c>
+      <c r="B437" t="s">
+        <v>5</v>
+      </c>
+      <c r="C437" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D437" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E437" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F437" t="s">
+        <v>62</v>
+      </c>
+      <c r="G437" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A438">
+        <v>437</v>
+      </c>
+      <c r="B438" t="s">
+        <v>5</v>
+      </c>
+      <c r="C438" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D438" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E438" t="s">
+        <v>1678</v>
+      </c>
+      <c r="F438" t="s">
+        <v>113</v>
+      </c>
+      <c r="G438" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A439">
+        <v>438</v>
+      </c>
+      <c r="B439" t="s">
+        <v>5</v>
+      </c>
+      <c r="C439" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D439" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E439" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F439" t="s">
+        <v>64</v>
+      </c>
+      <c r="G439" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A440">
+        <v>439</v>
+      </c>
+      <c r="B440" t="s">
+        <v>5</v>
+      </c>
+      <c r="C440" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D440" t="s">
+        <v>1695</v>
+      </c>
+      <c r="E440" t="s">
+        <v>1703</v>
+      </c>
+      <c r="F440" t="s">
+        <v>64</v>
+      </c>
+      <c r="G440" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A441">
+        <v>440</v>
+      </c>
+      <c r="B441" t="s">
+        <v>5</v>
+      </c>
+      <c r="C441" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D441" t="s">
+        <v>1696</v>
+      </c>
+      <c r="E441" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F441" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G441" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A442">
+        <v>441</v>
+      </c>
+      <c r="B442" t="s">
+        <v>5</v>
+      </c>
+      <c r="C442" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D442" t="s">
+        <v>1697</v>
+      </c>
+      <c r="E442" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F442" t="s">
+        <v>64</v>
+      </c>
+      <c r="G442" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A443">
+        <v>442</v>
+      </c>
+      <c r="B443" t="s">
+        <v>5</v>
+      </c>
+      <c r="C443" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D443" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E443" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F443" t="s">
+        <v>64</v>
+      </c>
+      <c r="G443" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A444">
+        <v>443</v>
+      </c>
+      <c r="B444" t="s">
+        <v>5</v>
+      </c>
+      <c r="C444" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D444" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E444" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F444" t="s">
+        <v>64</v>
+      </c>
+      <c r="G444" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A445">
+        <v>444</v>
+      </c>
+      <c r="B445" t="s">
+        <v>5</v>
+      </c>
+      <c r="C445" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D445" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E445" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F445" t="s">
+        <v>64</v>
+      </c>
+      <c r="G445" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A446">
+        <v>445</v>
+      </c>
+      <c r="B446" t="s">
+        <v>5</v>
+      </c>
+      <c r="C446" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D446" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E446" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F446" t="s">
+        <v>64</v>
+      </c>
+      <c r="G446" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A447">
+        <v>446</v>
+      </c>
+      <c r="B447" t="s">
+        <v>5</v>
+      </c>
+      <c r="C447" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D447" t="s">
+        <v>1719</v>
+      </c>
+      <c r="E447" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F447" t="s">
+        <v>114</v>
+      </c>
+      <c r="G447" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A448">
+        <v>447</v>
+      </c>
+      <c r="B448" t="s">
+        <v>5</v>
+      </c>
+      <c r="C448" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D448" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E448" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F448" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G448" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A449">
+        <v>448</v>
+      </c>
+      <c r="B449" t="s">
+        <v>5</v>
+      </c>
+      <c r="C449" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D449" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E449" t="s">
+        <v>1729</v>
+      </c>
+      <c r="F449" t="s">
+        <v>112</v>
+      </c>
+      <c r="G449" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A450">
+        <v>449</v>
+      </c>
+      <c r="B450" t="s">
+        <v>5</v>
+      </c>
+      <c r="C450" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D450" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E450" t="s">
+        <v>1730</v>
+      </c>
+      <c r="F450" t="s">
+        <v>112</v>
+      </c>
+      <c r="G450" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A451">
+        <v>450</v>
+      </c>
+      <c r="B451" t="s">
+        <v>5</v>
+      </c>
+      <c r="C451" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D451" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E451" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F451" t="s">
+        <v>112</v>
+      </c>
+      <c r="G451" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A452">
+        <v>451</v>
+      </c>
+      <c r="B452" t="s">
+        <v>5</v>
+      </c>
+      <c r="C452" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D452" t="s">
+        <v>1725</v>
+      </c>
+      <c r="E452" t="s">
+        <v>1732</v>
+      </c>
+      <c r="F452" t="s">
+        <v>112</v>
+      </c>
+      <c r="G452" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A453">
+        <v>452</v>
+      </c>
+      <c r="B453" t="s">
+        <v>5</v>
+      </c>
+      <c r="C453" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D453" t="s">
+        <v>1726</v>
+      </c>
+      <c r="E453" t="s">
+        <v>1733</v>
+      </c>
+      <c r="F453" t="s">
+        <v>112</v>
+      </c>
+      <c r="G453" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A454">
+        <v>453</v>
+      </c>
+      <c r="B454" t="s">
+        <v>5</v>
+      </c>
+      <c r="C454" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D454" t="s">
+        <v>1740</v>
+      </c>
+      <c r="E454" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F454" t="s">
+        <v>64</v>
+      </c>
+      <c r="G454" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A455">
+        <v>454</v>
+      </c>
+      <c r="B455" t="s">
+        <v>5</v>
+      </c>
+      <c r="C455" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D455" t="s">
+        <v>1741</v>
+      </c>
+      <c r="E455" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F455" t="s">
+        <v>112</v>
+      </c>
+      <c r="G455" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A456">
+        <v>455</v>
+      </c>
+      <c r="B456" t="s">
+        <v>5</v>
+      </c>
+      <c r="C456" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D456" t="s">
+        <v>1742</v>
+      </c>
+      <c r="E456" t="s">
+        <v>1754</v>
+      </c>
+      <c r="F456" t="s">
+        <v>112</v>
+      </c>
+      <c r="G456" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A457">
+        <v>456</v>
+      </c>
+      <c r="B457" t="s">
+        <v>5</v>
+      </c>
+      <c r="C457" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D457" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E457" t="s">
+        <v>1755</v>
+      </c>
+      <c r="F457" t="s">
+        <v>64</v>
+      </c>
+      <c r="G457" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A458">
+        <v>457</v>
+      </c>
+      <c r="B458" t="s">
+        <v>5</v>
+      </c>
+      <c r="C458" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D458" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E458" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F458" t="s">
+        <v>64</v>
+      </c>
+      <c r="G458" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A459">
+        <v>458</v>
+      </c>
+      <c r="B459" t="s">
+        <v>5</v>
+      </c>
+      <c r="C459" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D459" t="s">
+        <v>1748</v>
+      </c>
+      <c r="E459" t="s">
+        <v>1757</v>
+      </c>
+      <c r="F459" t="s">
+        <v>64</v>
+      </c>
+      <c r="G459" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A460">
+        <v>459</v>
+      </c>
+      <c r="B460" t="s">
+        <v>5</v>
+      </c>
+      <c r="C460" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D460" t="s">
+        <v>1749</v>
+      </c>
+      <c r="E460" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F460" t="s">
+        <v>112</v>
+      </c>
+      <c r="G460" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A461">
+        <v>460</v>
+      </c>
+      <c r="B461" t="s">
+        <v>5</v>
+      </c>
+      <c r="C461" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D461" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E461" t="s">
+        <v>1759</v>
+      </c>
+      <c r="F461" t="s">
+        <v>64</v>
+      </c>
+      <c r="G461" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A462">
+        <v>461</v>
+      </c>
+      <c r="B462" t="s">
+        <v>5</v>
+      </c>
+      <c r="C462" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D462" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E462" t="s">
+        <v>1782</v>
+      </c>
+      <c r="F462" t="s">
+        <v>64</v>
+      </c>
+      <c r="G462" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A463">
+        <v>462</v>
+      </c>
+      <c r="B463" t="s">
+        <v>5</v>
+      </c>
+      <c r="C463" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D463" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E463" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F463" t="s">
+        <v>112</v>
+      </c>
+      <c r="G463" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A464">
+        <v>463</v>
+      </c>
+      <c r="B464" t="s">
+        <v>5</v>
+      </c>
+      <c r="C464" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D464" t="s">
+        <v>1772</v>
+      </c>
+      <c r="E464" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F464" t="s">
+        <v>310</v>
+      </c>
+      <c r="G464" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A465">
+        <v>464</v>
+      </c>
+      <c r="B465" t="s">
+        <v>5</v>
+      </c>
+      <c r="C465" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D465" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E465" t="s">
+        <v>1785</v>
+      </c>
+      <c r="F465" t="s">
+        <v>112</v>
+      </c>
+      <c r="G465" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A466">
+        <v>465</v>
+      </c>
+      <c r="B466" t="s">
+        <v>5</v>
+      </c>
+      <c r="C466" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D466" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E466" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F466" t="s">
+        <v>278</v>
+      </c>
+      <c r="G466" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A467">
+        <v>466</v>
+      </c>
+      <c r="B467" t="s">
+        <v>5</v>
+      </c>
+      <c r="C467" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D467" t="s">
+        <v>1777</v>
+      </c>
+      <c r="E467" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F467" t="s">
+        <v>430</v>
+      </c>
+      <c r="G467" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A468">
+        <v>467</v>
+      </c>
+      <c r="B468" t="s">
+        <v>5</v>
+      </c>
+      <c r="C468" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D468" t="s">
+        <v>1779</v>
+      </c>
+      <c r="E468" t="s">
+        <v>1788</v>
+      </c>
+      <c r="F468" t="s">
+        <v>64</v>
+      </c>
+      <c r="G468" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A469">
+        <v>468</v>
+      </c>
+      <c r="B469" t="s">
+        <v>5</v>
+      </c>
+      <c r="C469" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D469" t="s">
+        <v>1781</v>
+      </c>
+      <c r="E469" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F469" t="s">
+        <v>310</v>
+      </c>
+      <c r="G469" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A470">
+        <v>469</v>
+      </c>
+      <c r="B470" t="s">
+        <v>5</v>
+      </c>
+      <c r="C470" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D470" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E470" t="s">
+        <v>1810</v>
+      </c>
+      <c r="F470" t="s">
+        <v>182</v>
+      </c>
+      <c r="G470" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A471">
+        <v>470</v>
+      </c>
+      <c r="B471" t="s">
+        <v>5</v>
+      </c>
+      <c r="C471" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D471" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E471" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F471" t="s">
+        <v>64</v>
+      </c>
+      <c r="G471" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A472">
+        <v>471</v>
+      </c>
+      <c r="B472" t="s">
+        <v>5</v>
+      </c>
+      <c r="C472" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D472" t="s">
+        <v>1802</v>
+      </c>
+      <c r="E472" t="s">
+        <v>1812</v>
+      </c>
+      <c r="F472" t="s">
+        <v>64</v>
+      </c>
+      <c r="G472" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A473">
+        <v>472</v>
+      </c>
+      <c r="B473" t="s">
+        <v>5</v>
+      </c>
+      <c r="C473" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D473" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E473" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F473" t="s">
+        <v>817</v>
+      </c>
+      <c r="G473" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A474">
+        <v>473</v>
+      </c>
+      <c r="B474" t="s">
+        <v>5</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D474" t="s">
+        <v>1805</v>
+      </c>
+      <c r="E474" t="s">
+        <v>1814</v>
+      </c>
+      <c r="F474" t="s">
+        <v>64</v>
+      </c>
+      <c r="G474" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A475">
+        <v>474</v>
+      </c>
+      <c r="B475" t="s">
+        <v>5</v>
+      </c>
+      <c r="C475" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D475" t="s">
+        <v>1807</v>
+      </c>
+      <c r="E475" t="s">
+        <v>1815</v>
+      </c>
+      <c r="F475" t="s">
+        <v>64</v>
+      </c>
+      <c r="G475" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A476">
+        <v>475</v>
+      </c>
+      <c r="B476" t="s">
+        <v>5</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D476" t="s">
+        <v>1809</v>
+      </c>
+      <c r="E476" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F476" t="s">
+        <v>1817</v>
+      </c>
+      <c r="G476" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A477">
+        <v>476</v>
+      </c>
+      <c r="B477" t="s">
+        <v>5</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D477" t="s">
+        <v>1826</v>
+      </c>
+      <c r="E477" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F477" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G477" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A478">
+        <v>477</v>
+      </c>
+      <c r="B478" t="s">
+        <v>5</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D478" t="s">
+        <v>1828</v>
+      </c>
+      <c r="E478" t="s">
+        <v>1840</v>
+      </c>
+      <c r="F478" t="s">
+        <v>64</v>
+      </c>
+      <c r="G478" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A479">
+        <v>478</v>
+      </c>
+      <c r="B479" t="s">
+        <v>5</v>
+      </c>
+      <c r="C479" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D479" t="s">
+        <v>1830</v>
+      </c>
+      <c r="E479" t="s">
+        <v>1841</v>
+      </c>
+      <c r="F479" t="s">
+        <v>62</v>
+      </c>
+      <c r="G479" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A480">
+        <v>479</v>
+      </c>
+      <c r="B480" t="s">
+        <v>5</v>
+      </c>
+      <c r="C480" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D480" t="s">
+        <v>1832</v>
+      </c>
+      <c r="E480" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F480" t="s">
+        <v>430</v>
+      </c>
+      <c r="G480" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A481">
+        <v>480</v>
+      </c>
+      <c r="B481" t="s">
+        <v>5</v>
+      </c>
+      <c r="C481" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D481" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E481" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F481" t="s">
+        <v>310</v>
+      </c>
+      <c r="G481" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A482">
+        <v>481</v>
+      </c>
+      <c r="B482" t="s">
+        <v>5</v>
+      </c>
+      <c r="C482" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D482" t="s">
+        <v>1836</v>
+      </c>
+      <c r="E482" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F482" t="s">
+        <v>64</v>
+      </c>
+      <c r="G482" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A483">
+        <v>482</v>
+      </c>
+      <c r="B483" t="s">
+        <v>5</v>
+      </c>
+      <c r="C483" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D483" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E483" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F483" t="s">
+        <v>113</v>
+      </c>
+      <c r="G483" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A484">
+        <v>483</v>
+      </c>
+      <c r="B484" t="s">
+        <v>5</v>
+      </c>
+      <c r="C484" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D484" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E484" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F484" t="s">
+        <v>64</v>
+      </c>
+      <c r="G484" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A485">
+        <v>484</v>
+      </c>
+      <c r="B485" t="s">
+        <v>5</v>
+      </c>
+      <c r="C485" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D485" t="s">
+        <v>1855</v>
+      </c>
+      <c r="E485" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F485" t="s">
+        <v>64</v>
+      </c>
+      <c r="G485" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A486">
+        <v>485</v>
+      </c>
+      <c r="B486" t="s">
+        <v>5</v>
+      </c>
+      <c r="C486" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D486" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E486" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F486" t="s">
+        <v>64</v>
+      </c>
+      <c r="G486" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A487">
+        <v>486</v>
+      </c>
+      <c r="B487" t="s">
+        <v>5</v>
+      </c>
+      <c r="C487" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D487" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E487" t="s">
+        <v>1870</v>
+      </c>
+      <c r="F487" t="s">
+        <v>112</v>
+      </c>
+      <c r="G487" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A488">
+        <v>487</v>
+      </c>
+      <c r="B488" t="s">
+        <v>5</v>
+      </c>
+      <c r="C488" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D488" t="s">
+        <v>1860</v>
+      </c>
+      <c r="E488" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F488" t="s">
+        <v>64</v>
+      </c>
+      <c r="G488" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A489">
+        <v>488</v>
+      </c>
+      <c r="B489" t="s">
+        <v>5</v>
+      </c>
+      <c r="C489" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D489" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E489" t="s">
+        <v>1872</v>
+      </c>
+      <c r="F489" t="s">
+        <v>64</v>
+      </c>
+      <c r="G489" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A490">
+        <v>489</v>
+      </c>
+      <c r="B490" t="s">
+        <v>5</v>
+      </c>
+      <c r="C490" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D490" t="s">
+        <v>1864</v>
+      </c>
+      <c r="E490" t="s">
+        <v>1873</v>
+      </c>
+      <c r="F490" t="s">
+        <v>270</v>
+      </c>
+      <c r="G490" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A491">
+        <v>490</v>
+      </c>
+      <c r="B491" t="s">
+        <v>5</v>
+      </c>
+      <c r="C491" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D491" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E491" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F491" t="s">
+        <v>430</v>
+      </c>
+      <c r="G491" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A492">
+        <v>491</v>
+      </c>
+      <c r="B492" t="s">
+        <v>5</v>
+      </c>
+      <c r="C492" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D492" t="s">
+        <v>1884</v>
+      </c>
+      <c r="E492" t="s">
+        <v>1896</v>
+      </c>
+      <c r="F492" t="s">
+        <v>64</v>
+      </c>
+      <c r="G492" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A493">
+        <v>492</v>
+      </c>
+      <c r="B493" t="s">
+        <v>5</v>
+      </c>
+      <c r="C493" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D493" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E493" t="s">
+        <v>1897</v>
+      </c>
+      <c r="F493" t="s">
+        <v>973</v>
+      </c>
+      <c r="G493" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A494">
+        <v>493</v>
+      </c>
+      <c r="B494" t="s">
+        <v>5</v>
+      </c>
+      <c r="C494" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D494" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E494" t="s">
+        <v>1898</v>
+      </c>
+      <c r="F494" t="s">
+        <v>64</v>
+      </c>
+      <c r="G494" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A495">
+        <v>494</v>
+      </c>
+      <c r="B495" t="s">
+        <v>5</v>
+      </c>
+      <c r="C495" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D495" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E495" t="s">
+        <v>1899</v>
+      </c>
+      <c r="F495" t="s">
+        <v>182</v>
+      </c>
+      <c r="G495" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A496">
+        <v>495</v>
+      </c>
+      <c r="B496" t="s">
+        <v>5</v>
+      </c>
+      <c r="C496" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D496" t="s">
+        <v>1892</v>
+      </c>
+      <c r="E496" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F496" t="s">
+        <v>64</v>
+      </c>
+      <c r="G496" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A497">
+        <v>496</v>
+      </c>
+      <c r="B497" t="s">
+        <v>5</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D497" t="s">
+        <v>1893</v>
+      </c>
+      <c r="E497" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F497" t="s">
+        <v>112</v>
+      </c>
+      <c r="G497" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A498">
+        <v>497</v>
+      </c>
+      <c r="B498" t="s">
+        <v>5</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D498" t="s">
+        <v>1894</v>
+      </c>
+      <c r="E498" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F498" t="s">
+        <v>112</v>
+      </c>
+      <c r="G498" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A499">
+        <v>498</v>
+      </c>
+      <c r="B499" t="s">
+        <v>5</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D499" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E499" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F499" t="s">
+        <v>430</v>
+      </c>
+      <c r="G499" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A500">
+        <v>499</v>
+      </c>
+      <c r="B500" t="s">
+        <v>5</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D500" t="s">
+        <v>1913</v>
+      </c>
+      <c r="E500" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F500" t="s">
+        <v>430</v>
+      </c>
+      <c r="G500" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A501">
+        <v>500</v>
+      </c>
+      <c r="B501" t="s">
+        <v>5</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D501" t="s">
+        <v>1916</v>
+      </c>
+      <c r="E501" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F501" t="s">
+        <v>310</v>
+      </c>
+      <c r="G501" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A502">
+        <v>501</v>
+      </c>
+      <c r="B502" t="s">
+        <v>5</v>
+      </c>
+      <c r="C502" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D502" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E502" t="s">
+        <v>1931</v>
+      </c>
+      <c r="F502" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G502" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A503">
+        <v>502</v>
+      </c>
+      <c r="B503" t="s">
+        <v>5</v>
+      </c>
+      <c r="C503" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D503" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E503" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F503" t="s">
+        <v>61</v>
+      </c>
+      <c r="G503" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A504">
+        <v>503</v>
+      </c>
+      <c r="B504" t="s">
+        <v>5</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D504" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E504" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F504" t="s">
+        <v>61</v>
+      </c>
+      <c r="G504" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A505">
+        <v>504</v>
+      </c>
+      <c r="B505" t="s">
+        <v>5</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D505" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E505" t="s">
+        <v>1933</v>
+      </c>
+      <c r="F505" t="s">
+        <v>64</v>
+      </c>
+      <c r="G505" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A506">
+        <v>505</v>
+      </c>
+      <c r="B506" t="s">
+        <v>5</v>
+      </c>
+      <c r="C506" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D506" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E506" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F506" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G506" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A507">
+        <v>506</v>
+      </c>
+      <c r="B507" t="s">
+        <v>5</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D507" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E507" t="s">
+        <v>1935</v>
+      </c>
+      <c r="F507" t="s">
+        <v>64</v>
+      </c>
+      <c r="G507" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A508">
+        <v>507</v>
+      </c>
+      <c r="B508" t="s">
+        <v>5</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D508" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E508" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F508" t="s">
+        <v>64</v>
+      </c>
+      <c r="G508" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A509">
+        <v>508</v>
+      </c>
+      <c r="B509" t="s">
+        <v>5</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D509" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E509" t="s">
+        <v>1957</v>
+      </c>
+      <c r="F509" t="s">
+        <v>62</v>
+      </c>
+      <c r="G509" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A510">
+        <v>509</v>
+      </c>
+      <c r="B510" t="s">
+        <v>5</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D510" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E510" t="s">
+        <v>1958</v>
+      </c>
+      <c r="F510" t="s">
+        <v>113</v>
+      </c>
+      <c r="G510" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A511">
+        <v>510</v>
+      </c>
+      <c r="B511" t="s">
+        <v>5</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D511" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E511" t="s">
+        <v>1959</v>
+      </c>
+      <c r="F511" t="s">
+        <v>64</v>
+      </c>
+      <c r="G511" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A512">
+        <v>511</v>
+      </c>
+      <c r="B512" t="s">
+        <v>5</v>
+      </c>
+      <c r="C512" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D512" t="s">
+        <v>1951</v>
+      </c>
+      <c r="E512" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F512" t="s">
+        <v>310</v>
+      </c>
+      <c r="G512" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A513">
+        <v>512</v>
+      </c>
+      <c r="B513" t="s">
+        <v>5</v>
+      </c>
+      <c r="C513" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D513" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E513" t="s">
+        <v>1961</v>
+      </c>
+      <c r="F513" t="s">
+        <v>278</v>
+      </c>
+      <c r="G513" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A514">
+        <v>513</v>
+      </c>
+      <c r="B514" t="s">
+        <v>5</v>
+      </c>
+      <c r="C514" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D514" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E514" t="s">
+        <v>1962</v>
+      </c>
+      <c r="F514" t="s">
+        <v>64</v>
+      </c>
+      <c r="G514" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A515">
+        <v>514</v>
+      </c>
+      <c r="B515" t="s">
+        <v>5</v>
+      </c>
+      <c r="C515" t="s">
+        <v>1970</v>
+      </c>
+      <c r="D515" t="s">
+        <v>1971</v>
+      </c>
+      <c r="E515" t="s">
+        <v>1982</v>
+      </c>
+      <c r="F515" t="s">
+        <v>64</v>
+      </c>
+      <c r="G515" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A516">
+        <v>515</v>
+      </c>
+      <c r="B516" t="s">
+        <v>5</v>
+      </c>
+      <c r="C516" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D516" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E516" t="s">
+        <v>1983</v>
+      </c>
+      <c r="F516" t="s">
+        <v>64</v>
+      </c>
+      <c r="G516" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A517">
+        <v>516</v>
+      </c>
+      <c r="B517" t="s">
+        <v>5</v>
+      </c>
+      <c r="C517" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D517" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E517" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F517" t="s">
+        <v>64</v>
+      </c>
+      <c r="G517" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A518">
+        <v>517</v>
+      </c>
+      <c r="B518" t="s">
+        <v>5</v>
+      </c>
+      <c r="C518" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D518" t="s">
+        <v>1975</v>
+      </c>
+      <c r="E518" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F518" t="s">
+        <v>63</v>
+      </c>
+      <c r="G518" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A519">
+        <v>518</v>
+      </c>
+      <c r="B519" t="s">
+        <v>5</v>
+      </c>
+      <c r="C519" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D519" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E519" t="s">
+        <v>1986</v>
+      </c>
+      <c r="F519" t="s">
+        <v>63</v>
+      </c>
+      <c r="G519" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A520">
+        <v>519</v>
+      </c>
+      <c r="B520" t="s">
+        <v>5</v>
+      </c>
+      <c r="C520" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D520" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E520" t="s">
+        <v>1987</v>
+      </c>
+      <c r="F520" t="s">
+        <v>63</v>
+      </c>
+      <c r="G520" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A521">
+        <v>520</v>
+      </c>
+      <c r="B521" t="s">
+        <v>5</v>
+      </c>
+      <c r="C521" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D521" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E521" t="s">
+        <v>1991</v>
+      </c>
+      <c r="F521" t="s">
+        <v>65</v>
+      </c>
+      <c r="G521" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A522">
+        <v>521</v>
+      </c>
+      <c r="B522" t="s">
+        <v>5</v>
+      </c>
+      <c r="C522" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D522" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E522" t="s">
+        <v>1988</v>
+      </c>
+      <c r="F522" t="s">
+        <v>64</v>
+      </c>
+      <c r="G522" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A523">
+        <v>522</v>
+      </c>
+      <c r="B523" t="s">
+        <v>5</v>
+      </c>
+      <c r="C523" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D523" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E523" t="s">
+        <v>1989</v>
+      </c>
+      <c r="F523" t="s">
+        <v>63</v>
+      </c>
+      <c r="G523" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A524">
+        <v>523</v>
+      </c>
+      <c r="B524" t="s">
+        <v>5</v>
+      </c>
+      <c r="C524" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D524" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E524" t="s">
+        <v>1990</v>
+      </c>
+      <c r="F524" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G524" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A525">
+        <v>524</v>
+      </c>
+      <c r="B525" t="s">
+        <v>5</v>
+      </c>
+      <c r="C525" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D525" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E525" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F525" t="s">
+        <v>64</v>
+      </c>
+      <c r="G525" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A526">
+        <v>525</v>
+      </c>
+      <c r="B526" t="s">
+        <v>5</v>
+      </c>
+      <c r="C526" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D526" t="s">
+        <v>2004</v>
+      </c>
+      <c r="E526" t="s">
+        <v>2017</v>
+      </c>
+      <c r="F526" t="s">
+        <v>182</v>
+      </c>
+      <c r="G526" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A527">
+        <v>526</v>
+      </c>
+      <c r="B527" t="s">
+        <v>5</v>
+      </c>
+      <c r="C527" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D527" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E527" t="s">
+        <v>2018</v>
+      </c>
+      <c r="F527" t="s">
+        <v>276</v>
+      </c>
+      <c r="G527" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A528">
+        <v>527</v>
+      </c>
+      <c r="B528" t="s">
+        <v>5</v>
+      </c>
+      <c r="C528" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D528" t="s">
+        <v>2008</v>
+      </c>
+      <c r="E528" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F528" t="s">
+        <v>64</v>
+      </c>
+      <c r="G528" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A529">
+        <v>528</v>
+      </c>
+      <c r="B529" t="s">
+        <v>5</v>
+      </c>
+      <c r="C529" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D529" t="s">
+        <v>2009</v>
+      </c>
+      <c r="E529" t="s">
+        <v>2020</v>
+      </c>
+      <c r="F529" t="s">
+        <v>112</v>
+      </c>
+      <c r="G529" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="530" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A530">
+        <v>529</v>
+      </c>
+      <c r="B530" t="s">
+        <v>5</v>
+      </c>
+      <c r="C530" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D530" t="s">
+        <v>2011</v>
+      </c>
+      <c r="E530" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F530" t="s">
+        <v>458</v>
+      </c>
+      <c r="G530" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A531">
+        <v>530</v>
+      </c>
+      <c r="B531" t="s">
+        <v>5</v>
+      </c>
+      <c r="C531" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D531" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E531" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F531" t="s">
+        <v>666</v>
+      </c>
+      <c r="G531" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A532">
+        <v>531</v>
+      </c>
+      <c r="B532" t="s">
+        <v>5</v>
+      </c>
+      <c r="C532" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D532" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E532" t="s">
+        <v>2023</v>
+      </c>
+      <c r="F532" t="s">
+        <v>270</v>
+      </c>
+      <c r="G532" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A533">
+        <v>532</v>
+      </c>
+      <c r="B533" t="s">
+        <v>5</v>
+      </c>
+      <c r="C533" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D533" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E533" t="s">
+        <v>2042</v>
+      </c>
+      <c r="F533" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G533" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A534">
+        <v>533</v>
+      </c>
+      <c r="B534" t="s">
+        <v>5</v>
+      </c>
+      <c r="C534" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D534" t="s">
+        <v>2034</v>
+      </c>
+      <c r="E534" t="s">
+        <v>2043</v>
+      </c>
+      <c r="F534" t="s">
+        <v>112</v>
+      </c>
+      <c r="G534" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A535">
+        <v>534</v>
+      </c>
+      <c r="B535" t="s">
+        <v>5</v>
+      </c>
+      <c r="C535" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D535" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E535" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F535" t="s">
+        <v>112</v>
+      </c>
+      <c r="G535" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A536">
+        <v>535</v>
+      </c>
+      <c r="B536" t="s">
+        <v>5</v>
+      </c>
+      <c r="C536" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D536" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E536" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F536" t="s">
+        <v>112</v>
+      </c>
+      <c r="G536" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A537">
+        <v>536</v>
+      </c>
+      <c r="B537" t="s">
+        <v>5</v>
+      </c>
+      <c r="C537" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D537" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E537" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F537" t="s">
+        <v>112</v>
+      </c>
+      <c r="G537" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A538">
+        <v>537</v>
+      </c>
+      <c r="B538" t="s">
+        <v>5</v>
+      </c>
+      <c r="C538" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D538" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E538" t="s">
+        <v>2047</v>
+      </c>
+      <c r="F538" t="s">
+        <v>113</v>
+      </c>
+      <c r="G538" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A539">
+        <v>538</v>
+      </c>
+      <c r="B539" t="s">
+        <v>5</v>
+      </c>
+      <c r="C539" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D539" t="s">
+        <v>2041</v>
+      </c>
+      <c r="E539" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F539" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G539" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A540">
+        <v>539</v>
+      </c>
+      <c r="B540" t="s">
+        <v>5</v>
+      </c>
+      <c r="C540" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D540" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E540" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F540" t="s">
+        <v>62</v>
+      </c>
+      <c r="G540" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A541">
+        <v>540</v>
+      </c>
+      <c r="B541" t="s">
+        <v>5</v>
+      </c>
+      <c r="C541" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D541" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E541" t="s">
+        <v>2070</v>
+      </c>
+      <c r="F541" t="s">
+        <v>64</v>
+      </c>
+      <c r="G541" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A542">
+        <v>541</v>
+      </c>
+      <c r="B542" t="s">
+        <v>5</v>
+      </c>
+      <c r="C542" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D542" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E542" t="s">
+        <v>2071</v>
+      </c>
+      <c r="F542" t="s">
+        <v>64</v>
+      </c>
+      <c r="G542" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A543">
+        <v>542</v>
+      </c>
+      <c r="B543" t="s">
+        <v>5</v>
+      </c>
+      <c r="C543" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D543" t="s">
+        <v>2062</v>
+      </c>
+      <c r="E543" t="s">
+        <v>2072</v>
+      </c>
+      <c r="F543" t="s">
+        <v>309</v>
+      </c>
+      <c r="G543" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A544">
+        <v>543</v>
+      </c>
+      <c r="B544" t="s">
+        <v>5</v>
+      </c>
+      <c r="C544" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D544" t="s">
+        <v>2064</v>
+      </c>
+      <c r="E544" t="s">
+        <v>2073</v>
+      </c>
+      <c r="F544" t="s">
+        <v>277</v>
+      </c>
+      <c r="G544" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A545">
+        <v>544</v>
+      </c>
+      <c r="B545" t="s">
+        <v>5</v>
+      </c>
+      <c r="C545" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D545" t="s">
+        <v>2066</v>
+      </c>
+      <c r="E545" t="s">
+        <v>2074</v>
+      </c>
+      <c r="F545" t="s">
+        <v>765</v>
+      </c>
+      <c r="G545" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A546">
+        <v>545</v>
+      </c>
+      <c r="B546" t="s">
+        <v>5</v>
+      </c>
+      <c r="C546" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D546" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E546" t="s">
+        <v>2075</v>
+      </c>
+      <c r="F546" t="s">
+        <v>458</v>
+      </c>
+      <c r="G546" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A547">
+        <v>546</v>
+      </c>
+      <c r="B547" t="s">
+        <v>5</v>
+      </c>
+      <c r="C547" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D547" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E547" t="s">
+        <v>2096</v>
+      </c>
+      <c r="F547" t="s">
+        <v>64</v>
+      </c>
+      <c r="G547" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="548" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A548">
+        <v>547</v>
+      </c>
+      <c r="B548" t="s">
+        <v>5</v>
+      </c>
+      <c r="C548" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D548" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E548" t="s">
+        <v>2097</v>
+      </c>
+      <c r="F548" t="s">
+        <v>62</v>
+      </c>
+      <c r="G548" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="549" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A549">
+        <v>548</v>
+      </c>
+      <c r="B549" t="s">
+        <v>5</v>
+      </c>
+      <c r="C549" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D549" t="s">
+        <v>2088</v>
+      </c>
+      <c r="E549" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F549" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G549" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="550" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A550">
+        <v>549</v>
+      </c>
+      <c r="B550" t="s">
+        <v>5</v>
+      </c>
+      <c r="C550" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D550" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E550" t="s">
+        <v>2099</v>
+      </c>
+      <c r="F550" t="s">
+        <v>112</v>
+      </c>
+      <c r="G550" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="551" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A551">
+        <v>550</v>
+      </c>
+      <c r="B551" t="s">
+        <v>5</v>
+      </c>
+      <c r="C551" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D551" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E551" t="s">
+        <v>2100</v>
+      </c>
+      <c r="F551" t="s">
+        <v>64</v>
+      </c>
+      <c r="G551" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="552" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A552">
+        <v>551</v>
+      </c>
+      <c r="B552" t="s">
+        <v>5</v>
+      </c>
+      <c r="C552" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D552" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E552" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F552" t="s">
+        <v>64</v>
+      </c>
+      <c r="G552" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A553">
+        <v>552</v>
+      </c>
+      <c r="B553" t="s">
+        <v>5</v>
+      </c>
+      <c r="C553" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D553" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E553" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F553" t="s">
+        <v>113</v>
+      </c>
+      <c r="G553" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A554">
+        <v>553</v>
+      </c>
+      <c r="B554" t="s">
+        <v>5</v>
+      </c>
+      <c r="C554" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D554" t="s">
+        <v>2112</v>
+      </c>
+      <c r="E554" t="s">
+        <v>2124</v>
+      </c>
+      <c r="F554" t="s">
+        <v>62</v>
+      </c>
+      <c r="G554" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A555">
+        <v>554</v>
+      </c>
+      <c r="B555" t="s">
+        <v>5</v>
+      </c>
+      <c r="C555" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D555" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E555" t="s">
+        <v>2125</v>
+      </c>
+      <c r="F555" t="s">
+        <v>64</v>
+      </c>
+      <c r="G555" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A556">
+        <v>555</v>
+      </c>
+      <c r="B556" t="s">
+        <v>5</v>
+      </c>
+      <c r="C556" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D556" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E556" t="s">
+        <v>2126</v>
+      </c>
+      <c r="F556" t="s">
+        <v>64</v>
+      </c>
+      <c r="G556" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="557" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A557">
+        <v>556</v>
+      </c>
+      <c r="B557" t="s">
+        <v>5</v>
+      </c>
+      <c r="C557" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D557" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E557" t="s">
+        <v>2127</v>
+      </c>
+      <c r="F557" t="s">
+        <v>114</v>
+      </c>
+      <c r="G557" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="558" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A558">
+        <v>557</v>
+      </c>
+      <c r="B558" t="s">
+        <v>5</v>
+      </c>
+      <c r="C558" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D558" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E558" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F558" t="s">
+        <v>64</v>
+      </c>
+      <c r="G558" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A559">
+        <v>558</v>
+      </c>
+      <c r="B559" t="s">
+        <v>5</v>
+      </c>
+      <c r="C559" t="s">
+        <v>2121</v>
+      </c>
+      <c r="D559" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E559" t="s">
+        <v>2129</v>
+      </c>
+      <c r="F559" t="s">
+        <v>112</v>
+      </c>
+      <c r="G559" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A560">
+        <v>559</v>
+      </c>
+      <c r="B560" t="s">
+        <v>5</v>
+      </c>
+      <c r="C560" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D560" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E560" t="s">
+        <v>2130</v>
+      </c>
+      <c r="F560" t="s">
+        <v>112</v>
+      </c>
+      <c r="G560" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A561">
+        <v>560</v>
+      </c>
+      <c r="B561" t="s">
+        <v>5</v>
+      </c>
+      <c r="C561" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D561" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E561" t="s">
+        <v>2131</v>
+      </c>
+      <c r="F561" t="s">
+        <v>112</v>
+      </c>
+      <c r="G561" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A562">
+        <v>561</v>
+      </c>
+      <c r="B562" t="s">
+        <v>5</v>
+      </c>
+      <c r="C562" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D562" t="s">
+        <v>2141</v>
+      </c>
+      <c r="E562" t="s">
+        <v>2153</v>
+      </c>
+      <c r="F562" t="s">
+        <v>64</v>
+      </c>
+      <c r="G562" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A563">
+        <v>562</v>
+      </c>
+      <c r="B563" t="s">
+        <v>5</v>
+      </c>
+      <c r="C563" t="s">
+        <v>2142</v>
+      </c>
+      <c r="D563" t="s">
+        <v>2143</v>
+      </c>
+      <c r="E563" t="s">
+        <v>2154</v>
+      </c>
+      <c r="F563" t="s">
+        <v>64</v>
+      </c>
+      <c r="G563" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A564">
+        <v>563</v>
+      </c>
+      <c r="B564" t="s">
+        <v>5</v>
+      </c>
+      <c r="C564" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D564" t="s">
+        <v>2144</v>
+      </c>
+      <c r="E564" t="s">
+        <v>2155</v>
+      </c>
+      <c r="F564" t="s">
+        <v>112</v>
+      </c>
+      <c r="G564" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A565">
+        <v>564</v>
+      </c>
+      <c r="B565" t="s">
+        <v>5</v>
+      </c>
+      <c r="C565" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D565" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E565" t="s">
+        <v>2156</v>
+      </c>
+      <c r="F565" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G565" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="566" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A566">
+        <v>565</v>
+      </c>
+      <c r="B566" t="s">
+        <v>5</v>
+      </c>
+      <c r="C566" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D566" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E566" t="s">
+        <v>2157</v>
+      </c>
+      <c r="F566" t="s">
+        <v>64</v>
+      </c>
+      <c r="G566" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A567">
+        <v>566</v>
+      </c>
+      <c r="B567" t="s">
+        <v>5</v>
+      </c>
+      <c r="C567" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D567" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E567" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F567" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G567" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A568">
+        <v>567</v>
+      </c>
+      <c r="B568" t="s">
+        <v>5</v>
+      </c>
+      <c r="C568" t="s">
+        <v>2150</v>
+      </c>
+      <c r="D568" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E568" t="s">
+        <v>2159</v>
+      </c>
+      <c r="F568" t="s">
+        <v>112</v>
+      </c>
+      <c r="G568" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A569">
+        <v>568</v>
+      </c>
+      <c r="B569" t="s">
+        <v>5</v>
+      </c>
+      <c r="C569" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D569" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E569" t="s">
+        <v>2160</v>
+      </c>
+      <c r="F569" t="s">
+        <v>64</v>
+      </c>
+      <c r="G569" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A570">
+        <v>569</v>
+      </c>
+      <c r="B570" t="s">
+        <v>5</v>
+      </c>
+      <c r="C570" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D570" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E570" t="s">
+        <v>2183</v>
+      </c>
+      <c r="F570" t="s">
+        <v>64</v>
+      </c>
+      <c r="G570" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A571">
+        <v>570</v>
+      </c>
+      <c r="B571" t="s">
+        <v>5</v>
+      </c>
+      <c r="C571" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D571" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E571" t="s">
+        <v>2184</v>
+      </c>
+      <c r="F571" t="s">
+        <v>666</v>
+      </c>
+      <c r="G571" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A572">
+        <v>571</v>
+      </c>
+      <c r="B572" t="s">
+        <v>5</v>
+      </c>
+      <c r="C572" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D572" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E572" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F572" t="s">
+        <v>973</v>
+      </c>
+      <c r="G572" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A573">
+        <v>572</v>
+      </c>
+      <c r="B573" t="s">
+        <v>5</v>
+      </c>
+      <c r="C573" t="s">
+        <v>2175</v>
+      </c>
+      <c r="D573" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E573" t="s">
+        <v>2186</v>
+      </c>
+      <c r="F573" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G573" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A574">
+        <v>573</v>
+      </c>
+      <c r="B574" t="s">
+        <v>5</v>
+      </c>
+      <c r="C574" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D574" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E574" t="s">
+        <v>2187</v>
+      </c>
+      <c r="F574" t="s">
+        <v>64</v>
+      </c>
+      <c r="G574" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A575">
+        <v>574</v>
+      </c>
+      <c r="B575" t="s">
+        <v>5</v>
+      </c>
+      <c r="C575" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D575" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E575" t="s">
+        <v>2188</v>
+      </c>
+      <c r="F575" t="s">
+        <v>64</v>
+      </c>
+      <c r="G575" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A576">
+        <v>575</v>
+      </c>
+      <c r="B576" t="s">
+        <v>5</v>
+      </c>
+      <c r="C576" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D576" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E576" t="s">
+        <v>2189</v>
+      </c>
+      <c r="F576" t="s">
+        <v>62</v>
+      </c>
+      <c r="G576" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A577">
+        <v>576</v>
+      </c>
+      <c r="B577" t="s">
+        <v>5</v>
+      </c>
+      <c r="C577" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D577" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E577" t="s">
+        <v>2210</v>
+      </c>
+      <c r="F577" t="s">
+        <v>64</v>
+      </c>
+      <c r="G577" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A578">
+        <v>577</v>
+      </c>
+      <c r="B578" t="s">
+        <v>5</v>
+      </c>
+      <c r="C578" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D578" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E578" t="s">
+        <v>2211</v>
+      </c>
+      <c r="F578" t="s">
+        <v>64</v>
+      </c>
+      <c r="G578" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A579">
+        <v>578</v>
+      </c>
+      <c r="B579" t="s">
+        <v>5</v>
+      </c>
+      <c r="C579" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D579" t="s">
+        <v>2202</v>
+      </c>
+      <c r="E579" t="s">
+        <v>2212</v>
+      </c>
+      <c r="F579" t="s">
+        <v>64</v>
+      </c>
+      <c r="G579" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="580" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A580">
+        <v>579</v>
+      </c>
+      <c r="B580" t="s">
+        <v>5</v>
+      </c>
+      <c r="C580" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D580" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E580" t="s">
+        <v>2213</v>
+      </c>
+      <c r="F580" t="s">
+        <v>113</v>
+      </c>
+      <c r="G580" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A581">
+        <v>580</v>
+      </c>
+      <c r="B581" t="s">
+        <v>5</v>
+      </c>
+      <c r="C581" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D581" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E581" t="s">
+        <v>2213</v>
+      </c>
+      <c r="F581" t="s">
+        <v>113</v>
+      </c>
+      <c r="G581" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A582">
+        <v>581</v>
+      </c>
+      <c r="B582" t="s">
+        <v>5</v>
+      </c>
+      <c r="C582" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D582" t="s">
+        <v>2207</v>
+      </c>
+      <c r="E582" t="s">
+        <v>2214</v>
+      </c>
+      <c r="F582" t="s">
+        <v>64</v>
+      </c>
+      <c r="G582" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A583">
+        <v>582</v>
+      </c>
+      <c r="B583" t="s">
+        <v>5</v>
+      </c>
+      <c r="C583" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D583" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E583" t="s">
+        <v>2215</v>
+      </c>
+      <c r="F583" t="s">
+        <v>64</v>
+      </c>
+      <c r="G583" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A584">
+        <v>583</v>
+      </c>
+      <c r="B584" t="s">
+        <v>5</v>
+      </c>
+      <c r="C584" t="s">
+        <v>2223</v>
+      </c>
+      <c r="D584" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E584" t="s">
+        <v>2232</v>
+      </c>
+      <c r="F584" t="s">
+        <v>64</v>
+      </c>
+      <c r="G584" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A585">
+        <v>584</v>
+      </c>
+      <c r="B585" t="s">
+        <v>5</v>
+      </c>
+      <c r="C585" t="s">
+        <v>705</v>
+      </c>
+      <c r="D585" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E585" t="s">
+        <v>2233</v>
+      </c>
+      <c r="F585" t="s">
+        <v>64</v>
+      </c>
+      <c r="G585" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A586">
+        <v>585</v>
+      </c>
+      <c r="B586" t="s">
+        <v>5</v>
+      </c>
+      <c r="C586" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D586" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E586" t="s">
+        <v>2234</v>
+      </c>
+      <c r="F586" t="s">
+        <v>309</v>
+      </c>
+      <c r="G586" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A587">
+        <v>586</v>
+      </c>
+      <c r="B587" t="s">
+        <v>5</v>
+      </c>
+      <c r="C587" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D587" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E587" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F587" t="s">
+        <v>113</v>
+      </c>
+      <c r="G587" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A588">
+        <v>587</v>
+      </c>
+      <c r="B588" t="s">
+        <v>5</v>
+      </c>
+      <c r="C588" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D588" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E588" t="s">
+        <v>2236</v>
+      </c>
+      <c r="F588" t="s">
+        <v>61</v>
+      </c>
+      <c r="G588" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A589">
+        <v>588</v>
+      </c>
+      <c r="B589" t="s">
+        <v>5</v>
+      </c>
+      <c r="C589" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D589" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E589" t="s">
+        <v>2236</v>
+      </c>
+      <c r="F589" t="s">
+        <v>61</v>
+      </c>
+      <c r="G589" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A590">
+        <v>589</v>
+      </c>
+      <c r="B590" t="s">
+        <v>5</v>
+      </c>
+      <c r="C590" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D590" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E590" t="s">
+        <v>2257</v>
+      </c>
+      <c r="F590" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G590" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A591">
+        <v>590</v>
+      </c>
+      <c r="B591" t="s">
+        <v>5</v>
+      </c>
+      <c r="C591" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D591" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E591" t="s">
+        <v>2258</v>
+      </c>
+      <c r="F591" t="s">
+        <v>64</v>
+      </c>
+      <c r="G591" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A592">
+        <v>591</v>
+      </c>
+      <c r="B592" t="s">
+        <v>5</v>
+      </c>
+      <c r="C592" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D592" t="s">
+        <v>2248</v>
+      </c>
+      <c r="E592" t="s">
+        <v>2259</v>
+      </c>
+      <c r="F592" t="s">
+        <v>113</v>
+      </c>
+      <c r="G592" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A593">
+        <v>592</v>
+      </c>
+      <c r="B593" t="s">
+        <v>5</v>
+      </c>
+      <c r="C593" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D593" t="s">
+        <v>2250</v>
+      </c>
+      <c r="E593" t="s">
+        <v>2260</v>
+      </c>
+      <c r="F593" t="s">
+        <v>62</v>
+      </c>
+      <c r="G593" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A594">
+        <v>593</v>
+      </c>
+      <c r="B594" t="s">
+        <v>5</v>
+      </c>
+      <c r="C594" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D594" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E594" t="s">
+        <v>2261</v>
+      </c>
+      <c r="F594" t="s">
+        <v>270</v>
+      </c>
+      <c r="G594" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A595">
+        <v>594</v>
+      </c>
+      <c r="B595" t="s">
+        <v>5</v>
+      </c>
+      <c r="C595" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D595" t="s">
+        <v>2254</v>
+      </c>
+      <c r="E595" t="s">
+        <v>2262</v>
+      </c>
+      <c r="F595" t="s">
+        <v>61</v>
+      </c>
+      <c r="G595" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A596">
+        <v>595</v>
+      </c>
+      <c r="B596" t="s">
+        <v>5</v>
+      </c>
+      <c r="C596" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D596" t="s">
+        <v>2256</v>
+      </c>
+      <c r="E596" t="s">
+        <v>2263</v>
+      </c>
+      <c r="F596" t="s">
+        <v>62</v>
+      </c>
+      <c r="G596" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A597">
+        <v>596</v>
+      </c>
+      <c r="B597" t="s">
+        <v>5</v>
+      </c>
+      <c r="C597" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D597" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E597" t="s">
+        <v>2281</v>
+      </c>
+      <c r="F597" t="s">
+        <v>973</v>
+      </c>
+      <c r="G597" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A598">
+        <v>597</v>
+      </c>
+      <c r="B598" t="s">
+        <v>5</v>
+      </c>
+      <c r="C598" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D598" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E598" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F598" t="s">
+        <v>309</v>
+      </c>
+      <c r="G598" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A599">
+        <v>598</v>
+      </c>
+      <c r="B599" t="s">
+        <v>5</v>
+      </c>
+      <c r="C599" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D599" t="s">
+        <v>2276</v>
+      </c>
+      <c r="E599" t="s">
+        <v>2283</v>
+      </c>
+      <c r="F599" t="s">
+        <v>64</v>
+      </c>
+      <c r="G599" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A600">
+        <v>599</v>
+      </c>
+      <c r="B600" t="s">
+        <v>5</v>
+      </c>
+      <c r="C600" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D600" t="s">
+        <v>2278</v>
+      </c>
+      <c r="E600" t="s">
+        <v>2284</v>
+      </c>
+      <c r="F600" t="s">
+        <v>113</v>
+      </c>
+      <c r="G600" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A601">
+        <v>600</v>
+      </c>
+      <c r="B601" t="s">
+        <v>5</v>
+      </c>
+      <c r="C601" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D601" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E601" t="s">
+        <v>2285</v>
+      </c>
+      <c r="F601" t="s">
+        <v>270</v>
+      </c>
+      <c r="G601" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A602">
+        <v>601</v>
+      </c>
+      <c r="B602" t="s">
+        <v>5</v>
+      </c>
+      <c r="C602" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D602" t="s">
+        <v>2293</v>
+      </c>
+      <c r="E602" t="s">
+        <v>2301</v>
+      </c>
+      <c r="F602" t="s">
+        <v>64</v>
+      </c>
+      <c r="G602" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A603">
+        <v>602</v>
+      </c>
+      <c r="B603" t="s">
+        <v>5</v>
+      </c>
+      <c r="C603" t="s">
+        <v>2292</v>
+      </c>
+      <c r="D603" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E603" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F603" t="s">
+        <v>62</v>
+      </c>
+      <c r="G603" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A604">
+        <v>603</v>
+      </c>
+      <c r="B604" t="s">
+        <v>5</v>
+      </c>
+      <c r="C604" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D604" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E604" t="s">
+        <v>2303</v>
+      </c>
+      <c r="F604" t="s">
+        <v>64</v>
+      </c>
+      <c r="G604" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A605">
+        <v>604</v>
+      </c>
+      <c r="B605" t="s">
+        <v>5</v>
+      </c>
+      <c r="C605" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D605" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E605" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F605" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G605" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A606">
+        <v>605</v>
+      </c>
+      <c r="B606" t="s">
+        <v>5</v>
+      </c>
+      <c r="C606" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D606" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E606" t="s">
+        <v>2305</v>
+      </c>
+      <c r="F606" t="s">
+        <v>64</v>
+      </c>
+      <c r="G606" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A607">
+        <v>606</v>
+      </c>
+      <c r="B607" t="s">
+        <v>5</v>
+      </c>
+      <c r="C607" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D607" t="s">
+        <v>2311</v>
+      </c>
+      <c r="E607" t="s">
+        <v>2320</v>
+      </c>
+      <c r="F607" t="s">
+        <v>2325</v>
+      </c>
+      <c r="G607" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A608">
+        <v>607</v>
+      </c>
+      <c r="B608" t="s">
+        <v>5</v>
+      </c>
+      <c r="C608" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D608" t="s">
+        <v>2313</v>
+      </c>
+      <c r="E608" t="s">
+        <v>2321</v>
+      </c>
+      <c r="F608" t="s">
+        <v>62</v>
+      </c>
+      <c r="G608" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A609">
+        <v>608</v>
+      </c>
+      <c r="B609" t="s">
+        <v>5</v>
+      </c>
+      <c r="C609" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D609" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E609" t="s">
+        <v>2322</v>
+      </c>
+      <c r="F609" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G609" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A610">
+        <v>609</v>
+      </c>
+      <c r="B610" t="s">
+        <v>5</v>
+      </c>
+      <c r="C610" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D610" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E610" t="s">
+        <v>2323</v>
+      </c>
+      <c r="F610" t="s">
+        <v>62</v>
+      </c>
+      <c r="G610" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A611">
+        <v>610</v>
+      </c>
+      <c r="B611" t="s">
+        <v>5</v>
+      </c>
+      <c r="C611" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D611" t="s">
+        <v>2316</v>
+      </c>
+      <c r="E611" t="s">
+        <v>2324</v>
+      </c>
+      <c r="F611" t="s">
+        <v>61</v>
+      </c>
+      <c r="G611" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A612">
+        <v>611</v>
+      </c>
+      <c r="B612" t="s">
+        <v>5</v>
+      </c>
+      <c r="C612" t="s">
+        <v>2318</v>
+      </c>
+      <c r="D612" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E612" t="s">
+        <v>2326</v>
+      </c>
+      <c r="F612" t="s">
+        <v>114</v>
+      </c>
+      <c r="G612" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="613" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A613">
+        <v>612</v>
+      </c>
+      <c r="B613" t="s">
+        <v>5</v>
+      </c>
+      <c r="C613" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D613" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E613" t="s">
+        <v>2347</v>
+      </c>
+      <c r="F613" t="s">
+        <v>63</v>
+      </c>
+      <c r="G613" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="614" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A614">
+        <v>613</v>
+      </c>
+      <c r="B614" t="s">
+        <v>5</v>
+      </c>
+      <c r="C614" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D614" t="s">
+        <v>2337</v>
+      </c>
+      <c r="E614" t="s">
+        <v>2348</v>
+      </c>
+      <c r="F614" t="s">
+        <v>113</v>
+      </c>
+      <c r="G614" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A615">
+        <v>614</v>
+      </c>
+      <c r="B615" t="s">
+        <v>5</v>
+      </c>
+      <c r="C615" t="s">
+        <v>2338</v>
+      </c>
+      <c r="D615" t="s">
+        <v>2339</v>
+      </c>
+      <c r="E615" t="s">
+        <v>2349</v>
+      </c>
+      <c r="F615" t="s">
+        <v>64</v>
+      </c>
+      <c r="G615" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A616">
+        <v>615</v>
+      </c>
+      <c r="B616" t="s">
+        <v>5</v>
+      </c>
+      <c r="C616" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D616" t="s">
+        <v>2341</v>
+      </c>
+      <c r="E616" t="s">
+        <v>2350</v>
+      </c>
+      <c r="F616" t="s">
+        <v>64</v>
+      </c>
+      <c r="G616" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A617">
+        <v>616</v>
+      </c>
+      <c r="B617" t="s">
+        <v>5</v>
+      </c>
+      <c r="C617" t="s">
+        <v>2342</v>
+      </c>
+      <c r="D617" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E617" t="s">
+        <v>2351</v>
+      </c>
+      <c r="F617" t="s">
+        <v>113</v>
+      </c>
+      <c r="G617" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A618">
+        <v>617</v>
+      </c>
+      <c r="B618" t="s">
+        <v>5</v>
+      </c>
+      <c r="C618" t="s">
+        <v>2343</v>
+      </c>
+      <c r="D618" t="s">
+        <v>2344</v>
+      </c>
+      <c r="E618" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F618" t="s">
+        <v>64</v>
+      </c>
+      <c r="G618" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A619">
+        <v>618</v>
+      </c>
+      <c r="B619" t="s">
+        <v>5</v>
+      </c>
+      <c r="C619" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D619" t="s">
+        <v>2346</v>
+      </c>
+      <c r="E619" t="s">
+        <v>2353</v>
+      </c>
+      <c r="F619" t="s">
+        <v>62</v>
+      </c>
+      <c r="G619" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A620">
+        <v>619</v>
+      </c>
+      <c r="B620" t="s">
+        <v>5</v>
+      </c>
+      <c r="C620" t="s">
+        <v>2361</v>
+      </c>
+      <c r="D620" t="s">
+        <v>2362</v>
+      </c>
+      <c r="E620" t="s">
+        <v>2375</v>
+      </c>
+      <c r="F620" t="s">
+        <v>62</v>
+      </c>
+      <c r="G620" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A621">
+        <v>620</v>
+      </c>
+      <c r="B621" t="s">
+        <v>5</v>
+      </c>
+      <c r="C621" t="s">
+        <v>2363</v>
+      </c>
+      <c r="D621" t="s">
+        <v>2364</v>
+      </c>
+      <c r="E621" t="s">
+        <v>2376</v>
+      </c>
+      <c r="F621" t="s">
+        <v>64</v>
+      </c>
+      <c r="G621" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A622">
+        <v>621</v>
+      </c>
+      <c r="B622" t="s">
+        <v>5</v>
+      </c>
+      <c r="C622" t="s">
+        <v>2365</v>
+      </c>
+      <c r="D622" t="s">
+        <v>2366</v>
+      </c>
+      <c r="E622" t="s">
+        <v>2377</v>
+      </c>
+      <c r="F622" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G622" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A623">
+        <v>622</v>
+      </c>
+      <c r="B623" t="s">
+        <v>5</v>
+      </c>
+      <c r="C623" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D623" t="s">
+        <v>2368</v>
+      </c>
+      <c r="E623" t="s">
+        <v>2378</v>
+      </c>
+      <c r="F623" t="s">
+        <v>430</v>
+      </c>
+      <c r="G623" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A624">
+        <v>623</v>
+      </c>
+      <c r="B624" t="s">
+        <v>5</v>
+      </c>
+      <c r="C624" t="s">
+        <v>2369</v>
+      </c>
+      <c r="D624" t="s">
+        <v>2370</v>
+      </c>
+      <c r="E624" t="s">
+        <v>2379</v>
+      </c>
+      <c r="F624" t="s">
+        <v>113</v>
+      </c>
+      <c r="G624" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A625">
+        <v>624</v>
+      </c>
+      <c r="B625" t="s">
+        <v>5</v>
+      </c>
+      <c r="C625" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D625" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E625" t="s">
+        <v>2380</v>
+      </c>
+      <c r="F625" t="s">
+        <v>62</v>
+      </c>
+      <c r="G625" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A626">
+        <v>625</v>
+      </c>
+      <c r="B626" t="s">
+        <v>5</v>
+      </c>
+      <c r="C626" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D626" t="s">
+        <v>2373</v>
+      </c>
+      <c r="E626" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F626" t="s">
+        <v>64</v>
+      </c>
+      <c r="G626" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A627">
+        <v>626</v>
+      </c>
+      <c r="B627" t="s">
+        <v>5</v>
+      </c>
+      <c r="C627" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D627" t="s">
+        <v>2389</v>
+      </c>
+      <c r="E627" t="s">
+        <v>2401</v>
+      </c>
+      <c r="F627" t="s">
+        <v>64</v>
+      </c>
+      <c r="G627" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A628">
+        <v>627</v>
+      </c>
+      <c r="B628" t="s">
+        <v>5</v>
+      </c>
+      <c r="C628" t="s">
+        <v>2390</v>
+      </c>
+      <c r="D628" t="s">
+        <v>2390</v>
+      </c>
+      <c r="E628" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F628" t="s">
+        <v>276</v>
+      </c>
+      <c r="G628" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A629">
+        <v>628</v>
+      </c>
+      <c r="B629" t="s">
+        <v>5</v>
+      </c>
+      <c r="C629" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D629" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E629" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F629" t="s">
+        <v>113</v>
+      </c>
+      <c r="G629" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A630">
+        <v>629</v>
+      </c>
+      <c r="B630" t="s">
+        <v>5</v>
+      </c>
+      <c r="C630" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D630" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E630" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F630" t="s">
+        <v>64</v>
+      </c>
+      <c r="G630" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A631">
+        <v>630</v>
+      </c>
+      <c r="B631" t="s">
+        <v>5</v>
+      </c>
+      <c r="C631" t="s">
+        <v>2395</v>
+      </c>
+      <c r="D631" t="s">
+        <v>2396</v>
+      </c>
+      <c r="E631" t="s">
+        <v>2405</v>
+      </c>
+      <c r="F631" t="s">
+        <v>430</v>
+      </c>
+      <c r="G631" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A632">
+        <v>631</v>
+      </c>
+      <c r="B632" t="s">
+        <v>5</v>
+      </c>
+      <c r="C632" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D632" t="s">
+        <v>2398</v>
+      </c>
+      <c r="E632" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F632" t="s">
+        <v>64</v>
+      </c>
+      <c r="G632" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A633">
+        <v>632</v>
+      </c>
+      <c r="B633" t="s">
+        <v>5</v>
+      </c>
+      <c r="C633" t="s">
+        <v>2399</v>
+      </c>
+      <c r="D633" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E633" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F633" t="s">
+        <v>64</v>
+      </c>
+      <c r="G633" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A634">
+        <v>633</v>
+      </c>
+      <c r="B634" t="s">
+        <v>5</v>
+      </c>
+      <c r="C634" t="s">
+        <v>2419</v>
+      </c>
+      <c r="D634" t="s">
+        <v>2420</v>
+      </c>
+      <c r="E634" t="s">
+        <v>2427</v>
+      </c>
+      <c r="F634" t="s">
+        <v>62</v>
+      </c>
+      <c r="G634" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A635">
+        <v>634</v>
+      </c>
+      <c r="B635" t="s">
+        <v>5</v>
+      </c>
+      <c r="C635" t="s">
+        <v>2414</v>
+      </c>
+      <c r="D635" t="s">
+        <v>2415</v>
+      </c>
+      <c r="E635" t="s">
+        <v>2428</v>
+      </c>
+      <c r="F635" t="s">
+        <v>64</v>
+      </c>
+      <c r="G635" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="636" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A636">
+        <v>635</v>
+      </c>
+      <c r="B636" t="s">
+        <v>5</v>
+      </c>
+      <c r="C636" t="s">
+        <v>2416</v>
+      </c>
+      <c r="D636" t="s">
+        <v>2416</v>
+      </c>
+      <c r="E636" t="s">
+        <v>2429</v>
+      </c>
+      <c r="F636" t="s">
+        <v>276</v>
+      </c>
+      <c r="G636" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="637" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A637">
+        <v>636</v>
+      </c>
+      <c r="B637" t="s">
+        <v>5</v>
+      </c>
+      <c r="C637" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D637" t="s">
+        <v>2418</v>
+      </c>
+      <c r="E637" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F637" t="s">
+        <v>64</v>
+      </c>
+      <c r="G637" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A638">
+        <v>637</v>
+      </c>
+      <c r="B638" t="s">
+        <v>5</v>
+      </c>
+      <c r="C638" t="s">
+        <v>2421</v>
+      </c>
+      <c r="D638" t="s">
+        <v>2422</v>
+      </c>
+      <c r="E638" t="s">
+        <v>2431</v>
+      </c>
+      <c r="F638" t="s">
+        <v>64</v>
+      </c>
+      <c r="G638" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="639" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A639">
+        <v>638</v>
+      </c>
+      <c r="B639" t="s">
+        <v>5</v>
+      </c>
+      <c r="C639" t="s">
+        <v>2423</v>
+      </c>
+      <c r="D639" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E639" t="s">
+        <v>2432</v>
+      </c>
+      <c r="F639" t="s">
+        <v>64</v>
+      </c>
+      <c r="G639" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="640" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A640">
+        <v>639</v>
+      </c>
+      <c r="B640" t="s">
+        <v>5</v>
+      </c>
+      <c r="C640" t="s">
+        <v>2425</v>
+      </c>
+      <c r="D640" t="s">
+        <v>2426</v>
+      </c>
+      <c r="E640" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F640" t="s">
+        <v>64</v>
+      </c>
+      <c r="G640" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="641" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A641">
+        <v>640</v>
+      </c>
+      <c r="B641" t="s">
+        <v>5</v>
+      </c>
+      <c r="C641" t="s">
+        <v>2441</v>
+      </c>
+      <c r="D641" t="s">
+        <v>2442</v>
+      </c>
+      <c r="E641" t="s">
+        <v>2449</v>
+      </c>
+      <c r="F641" t="s">
+        <v>458</v>
+      </c>
+      <c r="G641" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="642" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A642">
+        <v>641</v>
+      </c>
+      <c r="B642" t="s">
+        <v>5</v>
+      </c>
+      <c r="C642" t="s">
+        <v>2443</v>
+      </c>
+      <c r="D642" t="s">
+        <v>2444</v>
+      </c>
+      <c r="E642" t="s">
+        <v>2450</v>
+      </c>
+      <c r="F642" t="s">
+        <v>64</v>
+      </c>
+      <c r="G642" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="643" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A643">
+        <v>642</v>
+      </c>
+      <c r="B643" t="s">
+        <v>5</v>
+      </c>
+      <c r="C643" t="s">
+        <v>2445</v>
+      </c>
+      <c r="D643" t="s">
+        <v>2446</v>
+      </c>
+      <c r="E643" t="s">
+        <v>2451</v>
+      </c>
+      <c r="F643" t="s">
+        <v>724</v>
+      </c>
+      <c r="G643" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="644" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A644">
+        <v>643</v>
+      </c>
+      <c r="B644" t="s">
+        <v>5</v>
+      </c>
+      <c r="C644" t="s">
+        <v>2447</v>
+      </c>
+      <c r="D644" t="s">
+        <v>2447</v>
+      </c>
+      <c r="E644" t="s">
+        <v>1767</v>
+      </c>
+      <c r="F644" t="s">
+        <v>64</v>
+      </c>
+      <c r="G644" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="645" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A645">
+        <v>644</v>
+      </c>
+      <c r="B645" t="s">
+        <v>5</v>
+      </c>
+      <c r="C645" t="s">
+        <v>2448</v>
+      </c>
+      <c r="D645" t="s">
+        <v>2448</v>
+      </c>
+      <c r="E645" t="s">
+        <v>2452</v>
+      </c>
+      <c r="F645" t="s">
+        <v>112</v>
+      </c>
+      <c r="G645" t="s">
+        <v>2456</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
